--- a/ROSA_vitaSPEC/Results/test_pretraitements/ratio.beta.natif/Resultats_ratio.beta.natif_moy_diff.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/ratio.beta.natif/Resultats_ratio.beta.natif_moy_diff.xlsx
@@ -1,217 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U108-N806\Documents\STAGE_M2_ROSA_NIRS\VitaSPEC\vitaspec_R\ROSA_vitaSPEC\Results\test_pretraitements\ratio.beta.natif\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
-  <si>
-    <t>Pretraitement</t>
-  </si>
-  <si>
-    <t>LV1_diff</t>
-  </si>
-  <si>
-    <t>LV2_diff</t>
-  </si>
-  <si>
-    <t>LV3_diff</t>
-  </si>
-  <si>
-    <t>LV4_diff</t>
-  </si>
-  <si>
-    <t>LV5_diff</t>
-  </si>
-  <si>
-    <t>LV6_diff</t>
-  </si>
-  <si>
-    <t>LV7_diff</t>
-  </si>
-  <si>
-    <t>LV8_diff</t>
-  </si>
-  <si>
-    <t>LV9_diff</t>
-  </si>
-  <si>
-    <t>LV10_diff</t>
-  </si>
-  <si>
-    <t>LV11_diff</t>
-  </si>
-  <si>
-    <t>LV12_diff</t>
-  </si>
-  <si>
-    <t>LV13_diff</t>
-  </si>
-  <si>
-    <t>LV14_diff</t>
-  </si>
-  <si>
-    <t>LV15_diff</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1000,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,20,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,20,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,750,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,750,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_snv_sder_c(1,3,5)_</t>
-  </si>
-  <si>
-    <t>adj_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -223,13 +27,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -255,82 +52,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -372,7 +109,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -404,10 +141,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -439,7 +175,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -615,2373 +350,2485 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:P47"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="52.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="16" width="13.5703125" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>16</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Pretraitement</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>LV1_diff</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>LV2_diff</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>LV3_diff</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>LV4_diff</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>LV5_diff</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>LV6_diff</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>LV7_diff</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>LV8_diff</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>LV9_diff</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>LV10_diff</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>LV11_diff</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>LV12_diff</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>LV13_diff</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>LV14_diff</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>LV15_diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1000,1)_snv_</t>
+        </is>
       </c>
       <c r="B2">
-        <v>5.240827400998091E-2</v>
+        <v>0.05563109121187666</v>
       </c>
       <c r="C2">
-        <v>0.113729490323382</v>
+        <v>0.1141681418988816</v>
       </c>
       <c r="D2">
-        <v>0.13488961348808079</v>
+        <v>0.1350444710473837</v>
       </c>
       <c r="E2">
-        <v>0.13968679880280599</v>
+        <v>0.1349674012921784</v>
       </c>
       <c r="F2">
-        <v>0.19322804833426149</v>
+        <v>0.1884064406164</v>
       </c>
       <c r="G2">
-        <v>0.27633055545652868</v>
+        <v>0.2713196956808722</v>
       </c>
       <c r="H2">
-        <v>0.25877368745291718</v>
+        <v>0.2592310812832138</v>
       </c>
       <c r="I2">
-        <v>0.29818435681559002</v>
+        <v>0.2956790093407657</v>
       </c>
       <c r="J2">
-        <v>0.39624857004213448</v>
+        <v>0.38866178134463</v>
       </c>
       <c r="K2">
-        <v>0.38585461769067553</v>
+        <v>0.3838680453386865</v>
       </c>
       <c r="L2">
-        <v>0.41230224494526052</v>
+        <v>0.4192172857718994</v>
       </c>
       <c r="M2">
-        <v>0.44730926970413459</v>
+        <v>0.448640543181819</v>
       </c>
       <c r="N2">
-        <v>0.43847786240575909</v>
+        <v>0.438823116296888</v>
       </c>
       <c r="O2">
-        <v>0.42344676571063322</v>
+        <v>0.4247954252031472</v>
       </c>
       <c r="P2">
-        <v>0.41043953448898091</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>17</v>
+        <v>0.4087701776484949</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B3">
-        <v>5.5014414394831443E-2</v>
+        <v>0.05690719771576779</v>
       </c>
       <c r="C3">
-        <v>0.36069539667853101</v>
+        <v>0.3656741634320529</v>
       </c>
       <c r="D3">
-        <v>0.43518580429764259</v>
+        <v>0.4344263395684268</v>
       </c>
       <c r="E3">
-        <v>0.34021687201293538</v>
+        <v>0.3389676181624751</v>
       </c>
       <c r="F3">
-        <v>0.34097174601845243</v>
+        <v>0.3329328258166036</v>
       </c>
       <c r="G3">
-        <v>0.34287278919435921</v>
+        <v>0.3452363838127659</v>
       </c>
       <c r="H3">
-        <v>0.37577291359607379</v>
+        <v>0.3828228131874102</v>
       </c>
       <c r="I3">
-        <v>0.40347361818275701</v>
+        <v>0.413622321528216</v>
       </c>
       <c r="J3">
-        <v>0.40074789379982428</v>
+        <v>0.4145014783204052</v>
       </c>
       <c r="K3">
-        <v>0.40502340882743237</v>
+        <v>0.4224512782347168</v>
       </c>
       <c r="L3">
-        <v>0.44103165415203088</v>
+        <v>0.451740142258661</v>
       </c>
       <c r="M3">
-        <v>0.47800215260402951</v>
+        <v>0.491842887049267</v>
       </c>
       <c r="N3">
-        <v>0.54280443257536803</v>
+        <v>0.5551326739648299</v>
       </c>
       <c r="O3">
-        <v>0.60430961054865884</v>
+        <v>0.6050636996151983</v>
       </c>
       <c r="P3">
-        <v>0.60426253370661609</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>18</v>
+        <v>0.6049074430458261</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_</t>
+        </is>
       </c>
       <c r="B4">
-        <v>4.5724113999796208E-2</v>
+        <v>0.04494218362072765</v>
       </c>
       <c r="C4">
-        <v>7.3766334651449175E-2</v>
+        <v>0.06688501103216773</v>
       </c>
       <c r="D4">
-        <v>0.17460573463858231</v>
+        <v>0.1659928894240691</v>
       </c>
       <c r="E4">
-        <v>0.19764425766874499</v>
+        <v>0.1783569362423504</v>
       </c>
       <c r="F4">
-        <v>0.36082103773660601</v>
+        <v>0.3420239290087846</v>
       </c>
       <c r="G4">
-        <v>0.32468026785889359</v>
+        <v>0.3166177519659898</v>
       </c>
       <c r="H4">
-        <v>0.30314952337475948</v>
+        <v>0.285640315202581</v>
       </c>
       <c r="I4">
-        <v>0.36938035282353182</v>
+        <v>0.3525720787937666</v>
       </c>
       <c r="J4">
-        <v>0.41092239283410481</v>
+        <v>0.4000416086038757</v>
       </c>
       <c r="K4">
-        <v>0.43158968075397131</v>
+        <v>0.4349110002657984</v>
       </c>
       <c r="L4">
-        <v>0.44457021823648851</v>
+        <v>0.4424470332483901</v>
       </c>
       <c r="M4">
-        <v>0.43702866587951478</v>
+        <v>0.4372287183384281</v>
       </c>
       <c r="N4">
-        <v>0.44173270162085149</v>
+        <v>0.4407208696816092</v>
       </c>
       <c r="O4">
-        <v>0.4559716588958786</v>
+        <v>0.4540594255382683</v>
       </c>
       <c r="P4">
-        <v>0.49487924880116202</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>19</v>
+        <v>0.4903302276268759</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B5">
-        <v>4.2071941619026353E-2</v>
+        <v>0.04254617768974436</v>
       </c>
       <c r="C5">
-        <v>0.1574911152662325</v>
+        <v>0.1699115880435274</v>
       </c>
       <c r="D5">
-        <v>0.21036730061259371</v>
+        <v>0.2071950525689915</v>
       </c>
       <c r="E5">
-        <v>0.45653211089298451</v>
+        <v>0.4538816264250832</v>
       </c>
       <c r="F5">
-        <v>0.3234867869832968</v>
+        <v>0.3262911013825802</v>
       </c>
       <c r="G5">
-        <v>0.3767682525338758</v>
+        <v>0.383236599051708</v>
       </c>
       <c r="H5">
-        <v>0.39184606669425071</v>
+        <v>0.3972745928875171</v>
       </c>
       <c r="I5">
-        <v>0.39412076475075808</v>
+        <v>0.3945531675737108</v>
       </c>
       <c r="J5">
-        <v>0.35150447010595232</v>
+        <v>0.356258973089829</v>
       </c>
       <c r="K5">
-        <v>0.35250782456888852</v>
+        <v>0.3555555621927972</v>
       </c>
       <c r="L5">
-        <v>0.35985947351945569</v>
+        <v>0.3702601460736326</v>
       </c>
       <c r="M5">
-        <v>0.37768118006639217</v>
+        <v>0.3944217102994211</v>
       </c>
       <c r="N5">
-        <v>0.42450303781631632</v>
+        <v>0.4473828481461685</v>
       </c>
       <c r="O5">
-        <v>0.4590264315653681</v>
+        <v>0.4849359986018651</v>
       </c>
       <c r="P5">
-        <v>0.51131253026117029</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>20</v>
+        <v>0.5325513475458845</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
+        </is>
       </c>
       <c r="B6">
-        <v>4.0312110453458033E-2</v>
+        <v>0.04764650509638865</v>
       </c>
       <c r="C6">
-        <v>0.17965899838822699</v>
+        <v>0.183207882631748</v>
       </c>
       <c r="D6">
-        <v>0.1842480070023928</v>
+        <v>0.1866297060390134</v>
       </c>
       <c r="E6">
-        <v>0.444352178637342</v>
+        <v>0.4429769980657506</v>
       </c>
       <c r="F6">
-        <v>0.29294316496016992</v>
+        <v>0.2842376428696332</v>
       </c>
       <c r="G6">
-        <v>0.33382416840124141</v>
+        <v>0.3224976662723963</v>
       </c>
       <c r="H6">
-        <v>0.33792354722260559</v>
+        <v>0.3192029394550447</v>
       </c>
       <c r="I6">
-        <v>0.29158089024312189</v>
+        <v>0.2792322794247859</v>
       </c>
       <c r="J6">
-        <v>0.29075328185211219</v>
+        <v>0.2807275689283295</v>
       </c>
       <c r="K6">
-        <v>0.30215246465423301</v>
+        <v>0.2906071650731398</v>
       </c>
       <c r="L6">
-        <v>0.32427192381056108</v>
+        <v>0.3118124417371679</v>
       </c>
       <c r="M6">
-        <v>0.34196199018292489</v>
+        <v>0.3383141829451911</v>
       </c>
       <c r="N6">
-        <v>0.3745973141695344</v>
+        <v>0.3699205888630996</v>
       </c>
       <c r="O6">
-        <v>0.3878795227023904</v>
+        <v>0.3839209928119193</v>
       </c>
       <c r="P6">
-        <v>0.43586515440359619</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>21</v>
+        <v>0.4290510674750353</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_</t>
+        </is>
       </c>
       <c r="B7">
-        <v>4.6614768401833789E-2</v>
+        <v>0.05129048607482588</v>
       </c>
       <c r="C7">
-        <v>7.1368476151506266E-2</v>
+        <v>0.08026916604620876</v>
       </c>
       <c r="D7">
-        <v>0.15330713905754689</v>
+        <v>0.1622380121116061</v>
       </c>
       <c r="E7">
-        <v>0.1942716849718191</v>
+        <v>0.2048776581127008</v>
       </c>
       <c r="F7">
-        <v>0.32093898050505831</v>
+        <v>0.3265856479808825</v>
       </c>
       <c r="G7">
-        <v>0.36735521614260908</v>
+        <v>0.3756123723689413</v>
       </c>
       <c r="H7">
-        <v>0.32579481522504611</v>
+        <v>0.3348907868581779</v>
       </c>
       <c r="I7">
-        <v>0.30336729052399242</v>
+        <v>0.3017558244949132</v>
       </c>
       <c r="J7">
-        <v>0.36805715318692028</v>
+        <v>0.3701208929894783</v>
       </c>
       <c r="K7">
-        <v>0.40356099619680419</v>
+        <v>0.4095258209927923</v>
       </c>
       <c r="L7">
-        <v>0.43357416587528269</v>
+        <v>0.4476402903214154</v>
       </c>
       <c r="M7">
-        <v>0.45519664476113808</v>
+        <v>0.4678828626805808</v>
       </c>
       <c r="N7">
-        <v>0.42522364911272292</v>
+        <v>0.4359159498800375</v>
       </c>
       <c r="O7">
-        <v>0.44035456073193219</v>
+        <v>0.4430143221153206</v>
       </c>
       <c r="P7">
-        <v>0.45962315310613627</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>22</v>
+        <v>0.4633799388125083</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
+        </is>
       </c>
       <c r="B8">
-        <v>4.4680455302266553E-2</v>
+        <v>0.04470175764369676</v>
       </c>
       <c r="C8">
-        <v>7.9675587815395327E-2</v>
+        <v>0.07694034708910522</v>
       </c>
       <c r="D8">
-        <v>0.1832486143219666</v>
+        <v>0.174302974153233</v>
       </c>
       <c r="E8">
-        <v>0.33599631028130378</v>
+        <v>0.3311319338950985</v>
       </c>
       <c r="F8">
-        <v>0.32904106850327253</v>
+        <v>0.3175909284541064</v>
       </c>
       <c r="G8">
-        <v>0.2868000508893177</v>
+        <v>0.289680779771142</v>
       </c>
       <c r="H8">
-        <v>0.32336606785520139</v>
+        <v>0.3288111436757097</v>
       </c>
       <c r="I8">
-        <v>0.34745227646682059</v>
+        <v>0.34775625689759</v>
       </c>
       <c r="J8">
-        <v>0.35091258779093598</v>
+        <v>0.3606248465013536</v>
       </c>
       <c r="K8">
-        <v>0.37403879821292768</v>
+        <v>0.3772489238440932</v>
       </c>
       <c r="L8">
-        <v>0.4052419332861521</v>
+        <v>0.3966809285322583</v>
       </c>
       <c r="M8">
-        <v>0.39560295070705898</v>
+        <v>0.3934641598669181</v>
       </c>
       <c r="N8">
-        <v>0.38766155620643611</v>
+        <v>0.3885272226696632</v>
       </c>
       <c r="O8">
-        <v>0.40562188288069562</v>
+        <v>0.4049596406593578</v>
       </c>
       <c r="P8">
-        <v>0.43623583959452977</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>23</v>
+        <v>0.4399850292092309</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
+        </is>
       </c>
       <c r="B9">
-        <v>4.1738221570450713E-2</v>
+        <v>0.03913827910869513</v>
       </c>
       <c r="C9">
-        <v>7.2704498791262367E-2</v>
+        <v>0.07235782064911446</v>
       </c>
       <c r="D9">
-        <v>0.16208710884481081</v>
+        <v>0.1636434530230358</v>
       </c>
       <c r="E9">
-        <v>0.28712950274773769</v>
+        <v>0.2864773018512722</v>
       </c>
       <c r="F9">
-        <v>0.2808455522116598</v>
+        <v>0.2830164762182684</v>
       </c>
       <c r="G9">
-        <v>0.241856762810405</v>
+        <v>0.2420818136605644</v>
       </c>
       <c r="H9">
-        <v>0.27495906014112648</v>
+        <v>0.2683509765283728</v>
       </c>
       <c r="I9">
-        <v>0.2774689462867343</v>
+        <v>0.2722841378063341</v>
       </c>
       <c r="J9">
-        <v>0.27784015695678188</v>
+        <v>0.2756746887423166</v>
       </c>
       <c r="K9">
-        <v>0.28742901364551232</v>
+        <v>0.2809646024966752</v>
       </c>
       <c r="L9">
-        <v>0.32349213417819089</v>
+        <v>0.3167418973636862</v>
       </c>
       <c r="M9">
-        <v>0.29368203630332429</v>
+        <v>0.288820648432105</v>
       </c>
       <c r="N9">
-        <v>0.29740450107978128</v>
+        <v>0.2908494111471227</v>
       </c>
       <c r="O9">
-        <v>0.30839165892026821</v>
+        <v>0.3076989625299664</v>
       </c>
       <c r="P9">
-        <v>0.32883660751572957</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>24</v>
+        <v>0.3277006448445594</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
+        </is>
       </c>
       <c r="B10">
-        <v>4.6081969136088349E-2</v>
+        <v>0.04742784847370694</v>
       </c>
       <c r="C10">
-        <v>7.9747102533726577E-2</v>
+        <v>0.07592970546860947</v>
       </c>
       <c r="D10">
-        <v>0.1688029657809158</v>
+        <v>0.1655611608253206</v>
       </c>
       <c r="E10">
-        <v>0.30211536513056553</v>
+        <v>0.2965147460019969</v>
       </c>
       <c r="F10">
-        <v>0.29766748949997962</v>
+        <v>0.28863988315657</v>
       </c>
       <c r="G10">
-        <v>0.25100839764587829</v>
+        <v>0.2536556769020608</v>
       </c>
       <c r="H10">
-        <v>0.28034711875535517</v>
+        <v>0.2717997133197904</v>
       </c>
       <c r="I10">
-        <v>0.2737477105781746</v>
+        <v>0.2793942038953021</v>
       </c>
       <c r="J10">
-        <v>0.28415005603637189</v>
+        <v>0.2858822708258912</v>
       </c>
       <c r="K10">
-        <v>0.28556151426004228</v>
+        <v>0.2752615182132013</v>
       </c>
       <c r="L10">
-        <v>0.32990869779418169</v>
+        <v>0.3264273006355159</v>
       </c>
       <c r="M10">
-        <v>0.30265069672826411</v>
+        <v>0.2950863847206216</v>
       </c>
       <c r="N10">
-        <v>0.30649314693106822</v>
+        <v>0.2905058778256568</v>
       </c>
       <c r="O10">
-        <v>0.32059674996685672</v>
+        <v>0.3117439654784731</v>
       </c>
       <c r="P10">
-        <v>0.33804552987770148</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>25</v>
+        <v>0.3274816490644545</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B11">
-        <v>4.3039580067829153E-2</v>
+        <v>0.04276718134545312</v>
       </c>
       <c r="C11">
-        <v>7.432190581337178E-2</v>
+        <v>0.07648880988659193</v>
       </c>
       <c r="D11">
-        <v>0.1677149626610886</v>
+        <v>0.1720536324294984</v>
       </c>
       <c r="E11">
-        <v>0.28562607158038011</v>
+        <v>0.3049550503545099</v>
       </c>
       <c r="F11">
-        <v>0.28905283944492433</v>
+        <v>0.296933152773956</v>
       </c>
       <c r="G11">
-        <v>0.24738883443949861</v>
+        <v>0.247366030912389</v>
       </c>
       <c r="H11">
-        <v>0.28286398093247211</v>
+        <v>0.2831893855415533</v>
       </c>
       <c r="I11">
-        <v>0.28381190693660019</v>
+        <v>0.2798800743463626</v>
       </c>
       <c r="J11">
-        <v>0.29166426300751391</v>
+        <v>0.2855788937798672</v>
       </c>
       <c r="K11">
-        <v>0.28380709344683691</v>
+        <v>0.2809568941021483</v>
       </c>
       <c r="L11">
-        <v>0.3120510543983151</v>
+        <v>0.3117011848275794</v>
       </c>
       <c r="M11">
-        <v>0.28899210427400918</v>
+        <v>0.2921491830835295</v>
       </c>
       <c r="N11">
-        <v>0.28638733326778137</v>
+        <v>0.292696306757753</v>
       </c>
       <c r="O11">
-        <v>0.31124972339837342</v>
+        <v>0.3147100788722638</v>
       </c>
       <c r="P11">
-        <v>0.32192315769201152</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>26</v>
+        <v>0.32881059973584</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B12">
-        <v>4.9142174705079748E-2</v>
+        <v>0.04447619134397954</v>
       </c>
       <c r="C12">
-        <v>0.16713625117627659</v>
+        <v>0.1700666437450546</v>
       </c>
       <c r="D12">
-        <v>0.21224283455858381</v>
+        <v>0.2066130032248926</v>
       </c>
       <c r="E12">
-        <v>0.40361430453395303</v>
+        <v>0.4160587768563995</v>
       </c>
       <c r="F12">
-        <v>0.35171850251923592</v>
+        <v>0.3663780309195006</v>
       </c>
       <c r="G12">
-        <v>0.43794540619586497</v>
+        <v>0.4441601834519985</v>
       </c>
       <c r="H12">
-        <v>0.36535362592635812</v>
+        <v>0.3721502157690783</v>
       </c>
       <c r="I12">
-        <v>0.333484116557976</v>
+        <v>0.3329580972267034</v>
       </c>
       <c r="J12">
-        <v>0.31059547555404771</v>
+        <v>0.3090886126920661</v>
       </c>
       <c r="K12">
-        <v>0.30803424304890292</v>
+        <v>0.3063301053317433</v>
       </c>
       <c r="L12">
-        <v>0.32140470992963149</v>
+        <v>0.317731822002623</v>
       </c>
       <c r="M12">
-        <v>0.33679684925765441</v>
+        <v>0.3338393672699039</v>
       </c>
       <c r="N12">
-        <v>0.37933896321722183</v>
+        <v>0.3741825266275234</v>
       </c>
       <c r="O12">
-        <v>0.41222204644499488</v>
+        <v>0.4089364514923133</v>
       </c>
       <c r="P12">
-        <v>0.47822949585806512</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>27</v>
+        <v>0.4703620992886055</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
+        </is>
       </c>
       <c r="B13">
-        <v>5.8126603780969399E-2</v>
+        <v>0.06261050216397607</v>
       </c>
       <c r="C13">
-        <v>0.29496418519166973</v>
+        <v>0.2975907519866995</v>
       </c>
       <c r="D13">
-        <v>0.29778674960692142</v>
+        <v>0.2877311587416514</v>
       </c>
       <c r="E13">
-        <v>0.44584427510714653</v>
+        <v>0.4421020998829692</v>
       </c>
       <c r="F13">
-        <v>0.49253256830226022</v>
+        <v>0.4807896205755514</v>
       </c>
       <c r="G13">
-        <v>0.47486235275601679</v>
+        <v>0.4587878746696634</v>
       </c>
       <c r="H13">
-        <v>0.55477811294896884</v>
+        <v>0.5453248621813725</v>
       </c>
       <c r="I13">
-        <v>0.56280535581386981</v>
+        <v>0.55166780250654</v>
       </c>
       <c r="J13">
-        <v>0.54134513006543394</v>
+        <v>0.5438808607845338</v>
       </c>
       <c r="K13">
-        <v>0.51503152520422824</v>
+        <v>0.5147783048545211</v>
       </c>
       <c r="L13">
-        <v>0.52500574440788972</v>
+        <v>0.5273766197162721</v>
       </c>
       <c r="M13">
-        <v>0.53052748630739532</v>
+        <v>0.5395243343657288</v>
       </c>
       <c r="N13">
-        <v>0.54001595147927162</v>
+        <v>0.5459551209787161</v>
       </c>
       <c r="O13">
-        <v>0.54074032670749528</v>
+        <v>0.549683357996831</v>
       </c>
       <c r="P13">
-        <v>0.5701271506911304</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>28</v>
+        <v>0.5744811910495108</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+        </is>
       </c>
       <c r="B14">
-        <v>4.9447841504039559E-2</v>
+        <v>0.05027095809080803</v>
       </c>
       <c r="C14">
-        <v>7.5609577546818171E-2</v>
+        <v>0.07642322209012464</v>
       </c>
       <c r="D14">
-        <v>0.15344734580728581</v>
+        <v>0.1555281913516284</v>
       </c>
       <c r="E14">
-        <v>0.18569364018602411</v>
+        <v>0.1887445013009748</v>
       </c>
       <c r="F14">
-        <v>0.29546676870183658</v>
+        <v>0.3069170741815324</v>
       </c>
       <c r="G14">
-        <v>0.3358343967989052</v>
+        <v>0.3406115334704232</v>
       </c>
       <c r="H14">
-        <v>0.29292233308890608</v>
+        <v>0.3059682287476592</v>
       </c>
       <c r="I14">
-        <v>0.25549386726844869</v>
+        <v>0.2593974302832304</v>
       </c>
       <c r="J14">
-        <v>0.31395728329819561</v>
+        <v>0.3263866469108909</v>
       </c>
       <c r="K14">
-        <v>0.3473892128107775</v>
+        <v>0.3528932582879547</v>
       </c>
       <c r="L14">
-        <v>0.35555512779507892</v>
+        <v>0.3599363194579421</v>
       </c>
       <c r="M14">
-        <v>0.34486019399298001</v>
+        <v>0.348756503505362</v>
       </c>
       <c r="N14">
-        <v>0.32714737281493422</v>
+        <v>0.3337412098676963</v>
       </c>
       <c r="O14">
-        <v>0.32938689469421861</v>
+        <v>0.3396956056816117</v>
       </c>
       <c r="P14">
-        <v>0.3312942423603506</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>29</v>
+        <v>0.3361246407791394</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B15">
-        <v>5.1494020805196258E-2</v>
+        <v>0.05392207774531405</v>
       </c>
       <c r="C15">
-        <v>7.7149273840052615E-2</v>
+        <v>0.08037960362776046</v>
       </c>
       <c r="D15">
-        <v>0.1577818498579264</v>
+        <v>0.1584588310902402</v>
       </c>
       <c r="E15">
-        <v>0.18943032414270641</v>
+        <v>0.190038465642524</v>
       </c>
       <c r="F15">
-        <v>0.30355770143739802</v>
+        <v>0.3059757274329101</v>
       </c>
       <c r="G15">
-        <v>0.33516245611988188</v>
+        <v>0.3413622682736186</v>
       </c>
       <c r="H15">
-        <v>0.29802333722261698</v>
+        <v>0.2966005455390071</v>
       </c>
       <c r="I15">
-        <v>0.26438950032782799</v>
+        <v>0.2672207219621744</v>
       </c>
       <c r="J15">
-        <v>0.31324830982114471</v>
+        <v>0.3219843364678077</v>
       </c>
       <c r="K15">
-        <v>0.35460212115274131</v>
+        <v>0.3492516383106662</v>
       </c>
       <c r="L15">
-        <v>0.36746279413515942</v>
+        <v>0.3587061925465596</v>
       </c>
       <c r="M15">
-        <v>0.35399661886448802</v>
+        <v>0.3548177736867298</v>
       </c>
       <c r="N15">
-        <v>0.32878504917524071</v>
+        <v>0.3311109667694372</v>
       </c>
       <c r="O15">
-        <v>0.33225111063780338</v>
+        <v>0.339611065648223</v>
       </c>
       <c r="P15">
-        <v>0.33759781140864781</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>30</v>
+        <v>0.3385779703350835</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
+        </is>
       </c>
       <c r="B16">
-        <v>4.6362040573160193E-2</v>
+        <v>0.04664888461001213</v>
       </c>
       <c r="C16">
-        <v>7.4679006473765408E-2</v>
+        <v>0.07326891504712127</v>
       </c>
       <c r="D16">
-        <v>0.15703941343143971</v>
+        <v>0.1521185827590552</v>
       </c>
       <c r="E16">
-        <v>0.195828179627211</v>
+        <v>0.182514240441684</v>
       </c>
       <c r="F16">
-        <v>0.30892470640236108</v>
+        <v>0.290020099723902</v>
       </c>
       <c r="G16">
-        <v>0.34827434581241162</v>
+        <v>0.3365131760799979</v>
       </c>
       <c r="H16">
-        <v>0.30523593955323391</v>
+        <v>0.3047279497202995</v>
       </c>
       <c r="I16">
-        <v>0.26993276420549439</v>
+        <v>0.257137786272208</v>
       </c>
       <c r="J16">
-        <v>0.32123734040782448</v>
+        <v>0.3051574331953153</v>
       </c>
       <c r="K16">
-        <v>0.36093340858544021</v>
+        <v>0.3417476173633757</v>
       </c>
       <c r="L16">
-        <v>0.36909813490238652</v>
+        <v>0.3595511662701086</v>
       </c>
       <c r="M16">
-        <v>0.35652667429867108</v>
+        <v>0.3522203621096304</v>
       </c>
       <c r="N16">
-        <v>0.33540389263247061</v>
+        <v>0.3240611020332532</v>
       </c>
       <c r="O16">
-        <v>0.33589391182551848</v>
+        <v>0.3249415704943849</v>
       </c>
       <c r="P16">
-        <v>0.32795711790391707</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>31</v>
+        <v>0.329710347113119</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+        </is>
       </c>
       <c r="B17">
-        <v>4.7228476809482153E-2</v>
+        <v>0.04790643100872283</v>
       </c>
       <c r="C17">
-        <v>7.6205255860020485E-2</v>
+        <v>0.07686522950475097</v>
       </c>
       <c r="D17">
-        <v>0.15468753495241369</v>
+        <v>0.1576864453582564</v>
       </c>
       <c r="E17">
-        <v>0.19286920744308139</v>
+        <v>0.191013894355692</v>
       </c>
       <c r="F17">
-        <v>0.30007243313661103</v>
+        <v>0.289548863418194</v>
       </c>
       <c r="G17">
-        <v>0.3354536730256894</v>
+        <v>0.3366530547772572</v>
       </c>
       <c r="H17">
-        <v>0.3002867969108603</v>
+        <v>0.297143744278497</v>
       </c>
       <c r="I17">
-        <v>0.25805018543420549</v>
+        <v>0.245833709477977</v>
       </c>
       <c r="J17">
-        <v>0.31285009487886728</v>
+        <v>0.3042249333866919</v>
       </c>
       <c r="K17">
-        <v>0.35550466245219497</v>
+        <v>0.3464284633457706</v>
       </c>
       <c r="L17">
-        <v>0.37295543840662931</v>
+        <v>0.3671391756407926</v>
       </c>
       <c r="M17">
-        <v>0.3590976473331946</v>
+        <v>0.3521233180816149</v>
       </c>
       <c r="N17">
-        <v>0.33822471990533959</v>
+        <v>0.3436127231159527</v>
       </c>
       <c r="O17">
-        <v>0.33973133560059993</v>
+        <v>0.3500620387040658</v>
       </c>
       <c r="P17">
-        <v>0.3404979091692994</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>32</v>
+        <v>0.3533993865842961</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B18">
-        <v>4.6082367400867033E-2</v>
+        <v>0.04304763026957647</v>
       </c>
       <c r="C18">
-        <v>0.16606864299325641</v>
+        <v>0.1735714312457759</v>
       </c>
       <c r="D18">
-        <v>0.22358802801965039</v>
+        <v>0.2151166860059256</v>
       </c>
       <c r="E18">
-        <v>0.43009524398128818</v>
+        <v>0.4334453091851413</v>
       </c>
       <c r="F18">
-        <v>0.34405634944477909</v>
+        <v>0.3318260239118915</v>
       </c>
       <c r="G18">
-        <v>0.40477615640771619</v>
+        <v>0.3939112472911001</v>
       </c>
       <c r="H18">
-        <v>0.44458151355555908</v>
+        <v>0.4380192541253982</v>
       </c>
       <c r="I18">
-        <v>0.37986998377534242</v>
+        <v>0.3757840428054824</v>
       </c>
       <c r="J18">
-        <v>0.32872972579345638</v>
+        <v>0.327251317269264</v>
       </c>
       <c r="K18">
-        <v>0.31447918656113882</v>
+        <v>0.3181851484333762</v>
       </c>
       <c r="L18">
-        <v>0.34231012915523068</v>
+        <v>0.3409100480689309</v>
       </c>
       <c r="M18">
-        <v>0.35865516926376401</v>
+        <v>0.3532559724747234</v>
       </c>
       <c r="N18">
-        <v>0.40788395029031699</v>
+        <v>0.4072002027541485</v>
       </c>
       <c r="O18">
-        <v>0.4507089495353192</v>
+        <v>0.4520461519661561</v>
       </c>
       <c r="P18">
-        <v>0.49102076440231629</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>33</v>
+        <v>0.4940222878048772</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
+        </is>
       </c>
       <c r="B19">
-        <v>4.599141658294284E-2</v>
+        <v>0.04417430208801208</v>
       </c>
       <c r="C19">
-        <v>0.19060842076254031</v>
+        <v>0.1958710567660968</v>
       </c>
       <c r="D19">
-        <v>0.2087277354436953</v>
+        <v>0.2109897303077429</v>
       </c>
       <c r="E19">
-        <v>0.44678318629391062</v>
+        <v>0.4617027682871864</v>
       </c>
       <c r="F19">
-        <v>0.29129699083395949</v>
+        <v>0.3020456258756548</v>
       </c>
       <c r="G19">
-        <v>0.30865054675808518</v>
+        <v>0.3174250610331316</v>
       </c>
       <c r="H19">
-        <v>0.27922257264289091</v>
+        <v>0.2820043288851228</v>
       </c>
       <c r="I19">
-        <v>0.2645380579537287</v>
+        <v>0.268434856376719</v>
       </c>
       <c r="J19">
-        <v>0.25626819988974803</v>
+        <v>0.2655374724131535</v>
       </c>
       <c r="K19">
-        <v>0.27632911225161982</v>
-      </c>
-      <c r="L19" s="2">
-        <v>0.30558014067478351</v>
+        <v>0.2844623695912794</v>
+      </c>
+      <c r="L19">
+        <v>0.308796876942658</v>
       </c>
       <c r="M19">
-        <v>0.33304049583574658</v>
+        <v>0.3327964419287646</v>
       </c>
       <c r="N19">
-        <v>0.37764416186767269</v>
+        <v>0.3705356140094983</v>
       </c>
       <c r="O19">
-        <v>0.38398327809673932</v>
+        <v>0.3819874769173189</v>
       </c>
       <c r="P19">
-        <v>0.41773652972648578</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>34</v>
+        <v>0.4193121638008007</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+        </is>
       </c>
       <c r="B20">
-        <v>4.5673206265316582E-2</v>
+        <v>0.04284921055280411</v>
       </c>
       <c r="C20">
-        <v>0.24518195570028001</v>
+        <v>0.2339946617047228</v>
       </c>
       <c r="D20">
-        <v>0.22591216804360389</v>
+        <v>0.2269782832932368</v>
       </c>
       <c r="E20">
-        <v>0.25419034875033142</v>
+        <v>0.258466559153569</v>
       </c>
       <c r="F20">
-        <v>0.2414049443317213</v>
+        <v>0.2541150575331637</v>
       </c>
       <c r="G20">
-        <v>0.31325722135551559</v>
+        <v>0.3376126165980767</v>
       </c>
       <c r="H20">
-        <v>0.27680466548409149</v>
+        <v>0.2911449608697473</v>
       </c>
       <c r="I20">
-        <v>0.27235619821897122</v>
+        <v>0.2821159710633155</v>
       </c>
       <c r="J20">
-        <v>0.25904436742496217</v>
+        <v>0.2662891773550177</v>
       </c>
       <c r="K20">
-        <v>0.2776598367599416</v>
+        <v>0.2895538165060701</v>
       </c>
       <c r="L20">
-        <v>0.30698288191009798</v>
+        <v>0.3160419586963635</v>
       </c>
       <c r="M20">
-        <v>0.33927167773721251</v>
+        <v>0.3502621071878613</v>
       </c>
       <c r="N20">
-        <v>0.31858812606838172</v>
+        <v>0.3307697432820604</v>
       </c>
       <c r="O20">
-        <v>0.34136890189996172</v>
+        <v>0.3531120088106149</v>
       </c>
       <c r="P20">
-        <v>0.35523317152156092</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>35</v>
+        <v>0.3743896187317929</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B21">
-        <v>5.8471572305564212E-2</v>
+        <v>0.05653671480929614</v>
       </c>
       <c r="C21">
-        <v>0.33126251910423588</v>
+        <v>0.338060457377255</v>
       </c>
       <c r="D21">
-        <v>0.39029798671930072</v>
+        <v>0.4042615311971539</v>
       </c>
       <c r="E21">
-        <v>0.30794220328855693</v>
+        <v>0.3335062605363158</v>
       </c>
       <c r="F21">
-        <v>0.31842596867096551</v>
+        <v>0.3326134881511971</v>
       </c>
       <c r="G21">
-        <v>0.36566656344942278</v>
+        <v>0.3752173042017648</v>
       </c>
       <c r="H21">
-        <v>0.42811097127184711</v>
+        <v>0.429243526268769</v>
       </c>
       <c r="I21">
-        <v>0.44188497332565529</v>
+        <v>0.4609472623731067</v>
       </c>
       <c r="J21">
-        <v>0.43436464489627041</v>
+        <v>0.4328565958281415</v>
       </c>
       <c r="K21">
-        <v>0.43813459024981122</v>
+        <v>0.4434765708249782</v>
       </c>
       <c r="L21">
-        <v>0.45544902525354458</v>
+        <v>0.4595674181720638</v>
       </c>
       <c r="M21">
-        <v>0.5008033624816064</v>
+        <v>0.5028969284896093</v>
       </c>
       <c r="N21">
-        <v>0.57142897400530801</v>
+        <v>0.5656593334519245</v>
       </c>
       <c r="O21">
-        <v>0.63424711194023597</v>
+        <v>0.626010475226663</v>
       </c>
       <c r="P21">
-        <v>0.64583591613915114</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>36</v>
+        <v>0.6355569504279895</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B22">
-        <v>5.3183115662624167E-2</v>
+        <v>0.05644391737128929</v>
       </c>
       <c r="C22">
-        <v>0.33138590313558941</v>
+        <v>0.3365538355449278</v>
       </c>
       <c r="D22">
-        <v>0.38348091326011552</v>
+        <v>0.394856356624914</v>
       </c>
       <c r="E22">
-        <v>0.30897780635042971</v>
+        <v>0.3088040259873936</v>
       </c>
       <c r="F22">
-        <v>0.310563921738918</v>
+        <v>0.3147724370078919</v>
       </c>
       <c r="G22">
-        <v>0.35568286443261021</v>
+        <v>0.3594051589939151</v>
       </c>
       <c r="H22">
-        <v>0.43197124054244312</v>
+        <v>0.4359646447975319</v>
       </c>
       <c r="I22">
-        <v>0.4743197990231931</v>
+        <v>0.4849489258923366</v>
       </c>
       <c r="J22">
-        <v>0.46370565268617159</v>
+        <v>0.4744710263679416</v>
       </c>
       <c r="K22">
-        <v>0.46698217180488688</v>
+        <v>0.4827262931210594</v>
       </c>
       <c r="L22">
-        <v>0.50641830700040491</v>
+        <v>0.5206850334384707</v>
       </c>
       <c r="M22">
-        <v>0.53344941630348197</v>
+        <v>0.5484138366106824</v>
       </c>
       <c r="N22">
-        <v>0.58427040784803363</v>
+        <v>0.6012456621385573</v>
       </c>
       <c r="O22">
-        <v>0.60975957480238829</v>
+        <v>0.6271378139626057</v>
       </c>
       <c r="P22">
-        <v>0.628499936411405</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>37</v>
+        <v>0.6461711709746838</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B23">
-        <v>4.9275483418204508E-2</v>
+        <v>0.04486747003956511</v>
       </c>
       <c r="C23">
-        <v>0.26552109630061671</v>
+        <v>0.2622818540564522</v>
       </c>
       <c r="D23">
-        <v>0.28517819045695803</v>
+        <v>0.2650069795290623</v>
       </c>
       <c r="E23">
-        <v>0.2188254834963361</v>
+        <v>0.2181585693451353</v>
       </c>
       <c r="F23">
-        <v>0.29510983946670161</v>
+        <v>0.2884794746959213</v>
       </c>
       <c r="G23">
-        <v>0.28907656205859478</v>
+        <v>0.2833511991024185</v>
       </c>
       <c r="H23">
-        <v>0.30576649595960392</v>
+        <v>0.301482298919881</v>
       </c>
       <c r="I23">
-        <v>0.35015751550684843</v>
+        <v>0.3450827149249729</v>
       </c>
       <c r="J23">
-        <v>0.36598996624453711</v>
+        <v>0.3662614776156694</v>
       </c>
       <c r="K23">
-        <v>0.42724250558457422</v>
+        <v>0.4315413717226039</v>
       </c>
       <c r="L23">
-        <v>0.46027770580206678</v>
+        <v>0.467731718005481</v>
       </c>
       <c r="M23">
-        <v>0.52493486656480615</v>
+        <v>0.5297507855581582</v>
       </c>
       <c r="N23">
-        <v>0.54533007551436152</v>
+        <v>0.5515475809591412</v>
       </c>
       <c r="O23">
-        <v>0.56187126289945089</v>
+        <v>0.5687978068628966</v>
       </c>
       <c r="P23">
-        <v>0.59827380070251623</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>38</v>
+        <v>0.6024408876620548</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>adj_red_c(950,20,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B24">
-        <v>0.1031939764810622</v>
+        <v>0.1034109198290691</v>
       </c>
       <c r="C24">
-        <v>0.14692781836832891</v>
+        <v>0.1469524185218946</v>
       </c>
       <c r="D24">
-        <v>0.1897407920815106</v>
+        <v>0.1977443190989291</v>
       </c>
       <c r="E24">
-        <v>0.28876950834545428</v>
+        <v>0.2964798032407699</v>
       </c>
       <c r="F24">
-        <v>0.38311445151155521</v>
+        <v>0.3894485419447792</v>
       </c>
       <c r="G24">
-        <v>0.57004624324035691</v>
+        <v>0.5807821546342697</v>
       </c>
       <c r="H24">
-        <v>0.59521512256054943</v>
+        <v>0.6054864430544089</v>
       </c>
       <c r="I24">
-        <v>0.68234949479207674</v>
+        <v>0.6949531437266794</v>
       </c>
       <c r="J24">
-        <v>0.79627943936240675</v>
+        <v>0.8073963829184222</v>
       </c>
       <c r="K24">
-        <v>0.99765539940101011</v>
+        <v>1.008876905866965</v>
       </c>
       <c r="L24">
-        <v>1.001779851912463</v>
+        <v>1.023589330527838</v>
       </c>
       <c r="M24">
-        <v>1.077530634112883</v>
+        <v>1.099647301209441</v>
       </c>
       <c r="N24">
-        <v>1.198407519540083</v>
+        <v>1.228509155281901</v>
       </c>
       <c r="O24">
-        <v>1.300244763972944</v>
+        <v>1.33114613992754</v>
       </c>
       <c r="P24">
-        <v>1.455668124411599</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>39</v>
+        <v>1.471373251064128</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>adj_red_c(950,20,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B25">
-        <v>0.24735535434792769</v>
+        <v>0.2382746641053781</v>
       </c>
       <c r="C25">
-        <v>0.35380454470271622</v>
+        <v>0.3444317422076331</v>
       </c>
       <c r="D25">
-        <v>0.40300227067362981</v>
+        <v>0.3954122272763885</v>
       </c>
       <c r="E25">
-        <v>0.41170881217561839</v>
+        <v>0.4093038213081667</v>
       </c>
       <c r="F25">
-        <v>0.62814842448265207</v>
+        <v>0.6148450878934525</v>
       </c>
       <c r="G25">
-        <v>0.75307227250305553</v>
+        <v>0.736706603103042</v>
       </c>
       <c r="H25">
-        <v>0.79913471073846631</v>
+        <v>0.7900602188212057</v>
       </c>
       <c r="I25">
-        <v>0.81998969324845628</v>
+        <v>0.8153819312873283</v>
       </c>
       <c r="J25">
-        <v>0.88268495492811738</v>
+        <v>0.8842218272049924</v>
       </c>
       <c r="K25">
-        <v>1.0191282916776041</v>
+        <v>1.027560154489822</v>
       </c>
       <c r="L25">
-        <v>1.1021694563215649</v>
+        <v>1.114209500206629</v>
       </c>
       <c r="M25">
-        <v>1.235503414218005</v>
+        <v>1.25034107070512</v>
       </c>
       <c r="N25">
-        <v>1.3725123689024661</v>
+        <v>1.39136208683369</v>
       </c>
       <c r="O25">
-        <v>1.4570900184360851</v>
+        <v>1.473406456493909</v>
       </c>
       <c r="P25">
-        <v>1.5250472990494059</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>40</v>
+        <v>1.530448475729935</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>adj_red_c(950,750,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B26">
-        <v>9.7408358259443661E-2</v>
+        <v>0.09908485819786719</v>
       </c>
       <c r="C26">
-        <v>0.15752318763808401</v>
+        <v>0.1550102912703344</v>
       </c>
       <c r="D26">
-        <v>0.12668905003658409</v>
+        <v>0.1305086878043848</v>
       </c>
       <c r="E26">
-        <v>0.14004903067178889</v>
+        <v>0.1436021321381574</v>
       </c>
       <c r="F26">
-        <v>0.24721147808387331</v>
+        <v>0.2495483526458516</v>
       </c>
       <c r="G26">
-        <v>0.24826457105697261</v>
+        <v>0.2568331439127735</v>
       </c>
       <c r="H26">
-        <v>0.27326343708325712</v>
+        <v>0.2823304008278617</v>
       </c>
       <c r="I26">
-        <v>0.34547517053568072</v>
+        <v>0.3427872652500851</v>
       </c>
       <c r="J26">
-        <v>0.35626769055470969</v>
+        <v>0.3576756294268326</v>
       </c>
       <c r="K26">
-        <v>0.41294863269869242</v>
+        <v>0.4051328874395745</v>
       </c>
       <c r="L26">
-        <v>0.46265079722954289</v>
+        <v>0.457831044764084</v>
       </c>
       <c r="M26">
-        <v>0.47987736903762762</v>
+        <v>0.4727284300345447</v>
       </c>
       <c r="N26">
-        <v>0.52615594676355937</v>
+        <v>0.5318862209634109</v>
       </c>
       <c r="O26">
-        <v>0.61224465256226501</v>
+        <v>0.6094031571596334</v>
       </c>
       <c r="P26">
-        <v>0.63950813050067046</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>41</v>
+        <v>0.6407557102476871</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>adj_red_c(950,750,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B27">
-        <v>0.16706419081957691</v>
+        <v>0.1620646903971714</v>
       </c>
       <c r="C27">
-        <v>0.32045499041166092</v>
+        <v>0.3173437248974592</v>
       </c>
       <c r="D27">
-        <v>0.15081103113232749</v>
+        <v>0.1505623269748935</v>
       </c>
       <c r="E27">
-        <v>0.15997380764290131</v>
+        <v>0.1739876293255878</v>
       </c>
       <c r="F27">
-        <v>0.26410219390441197</v>
+        <v>0.2662164903437321</v>
       </c>
       <c r="G27">
-        <v>0.33017987536041538</v>
+        <v>0.3318972199762984</v>
       </c>
       <c r="H27">
-        <v>0.40190997179310711</v>
+        <v>0.4032100648351131</v>
       </c>
       <c r="I27">
-        <v>0.5474410043676935</v>
+        <v>0.5372374205235192</v>
       </c>
       <c r="J27">
-        <v>0.57545648574343788</v>
+        <v>0.5698576597860578</v>
       </c>
       <c r="K27">
-        <v>0.59789717326700009</v>
+        <v>0.5959062082355955</v>
       </c>
       <c r="L27">
-        <v>0.57322330082721984</v>
+        <v>0.5800082036153487</v>
       </c>
       <c r="M27">
-        <v>0.57371585837579542</v>
+        <v>0.5778430484343949</v>
       </c>
       <c r="N27">
-        <v>0.60372743704143295</v>
+        <v>0.6028297601976966</v>
       </c>
       <c r="O27">
-        <v>0.65721181928664163</v>
+        <v>0.6556481304555367</v>
       </c>
       <c r="P27">
-        <v>0.69539532558875816</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>42</v>
+        <v>0.6864757634299277</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
+        </is>
       </c>
       <c r="B28">
-        <v>6.6602283951884056E-2</v>
+        <v>0.06570764315186074</v>
       </c>
       <c r="C28">
-        <v>0.1230366003820058</v>
+        <v>0.1260303665767638</v>
       </c>
       <c r="D28">
-        <v>0.2195251382183061</v>
+        <v>0.217380376890624</v>
       </c>
       <c r="E28">
-        <v>0.20881124361886641</v>
+        <v>0.2095863268687897</v>
       </c>
       <c r="F28">
-        <v>0.22102606672162201</v>
+        <v>0.2254285865864742</v>
       </c>
       <c r="G28">
-        <v>0.21430886176133621</v>
+        <v>0.2137667510850345</v>
       </c>
       <c r="H28">
-        <v>0.30678689882396909</v>
+        <v>0.3045445112060176</v>
       </c>
       <c r="I28">
-        <v>0.44300433960782792</v>
+        <v>0.4374643034388481</v>
       </c>
       <c r="J28">
-        <v>0.47385902945308239</v>
+        <v>0.4846305620308974</v>
       </c>
       <c r="K28">
-        <v>0.46459635526981669</v>
+        <v>0.4613885173323259</v>
       </c>
       <c r="L28">
-        <v>0.47944336651951719</v>
+        <v>0.4767105780082181</v>
       </c>
       <c r="M28">
-        <v>0.56978983162857533</v>
+        <v>0.57354379191869</v>
       </c>
       <c r="N28">
-        <v>0.67814493296758038</v>
+        <v>0.6798900461119397</v>
       </c>
       <c r="O28">
-        <v>0.76074002028171483</v>
+        <v>0.7591500910769092</v>
       </c>
       <c r="P28">
-        <v>0.8624351218153945</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>43</v>
+        <v>0.86865358308392</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
+        </is>
       </c>
       <c r="B29">
-        <v>7.3280630697434249E-2</v>
+        <v>0.07468248532633814</v>
       </c>
       <c r="C29">
-        <v>0.13909679203366071</v>
+        <v>0.1371200004455143</v>
       </c>
       <c r="D29">
-        <v>0.24412153509201551</v>
+        <v>0.2419853731229922</v>
       </c>
       <c r="E29">
-        <v>0.23420966483259681</v>
+        <v>0.2322481430235171</v>
       </c>
       <c r="F29">
-        <v>0.2153616686273381</v>
+        <v>0.2193739351826484</v>
       </c>
       <c r="G29">
-        <v>0.24437044738025701</v>
+        <v>0.2470775924296489</v>
       </c>
       <c r="H29">
-        <v>0.54075168006617469</v>
+        <v>0.5331670501908701</v>
       </c>
       <c r="I29">
-        <v>0.53415759283756148</v>
+        <v>0.5106857265402862</v>
       </c>
       <c r="J29">
-        <v>0.51095442869727259</v>
+        <v>0.5036161824609836</v>
       </c>
       <c r="K29">
-        <v>0.48016698014620202</v>
+        <v>0.4850284201896578</v>
       </c>
       <c r="L29">
-        <v>0.48913719731722372</v>
+        <v>0.4860207788085383</v>
       </c>
       <c r="M29">
-        <v>0.52373122982823961</v>
+        <v>0.5190219676826066</v>
       </c>
       <c r="N29">
-        <v>0.60284362518482582</v>
+        <v>0.5983961790846576</v>
       </c>
       <c r="O29">
-        <v>0.69752578231737272</v>
+        <v>0.6919327640742713</v>
       </c>
       <c r="P29">
-        <v>0.7877413061949512</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>44</v>
+        <v>0.7774953912884077</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
+        </is>
       </c>
       <c r="B30">
-        <v>8.0339660867348547E-2</v>
+        <v>0.07758479740413186</v>
       </c>
       <c r="C30">
-        <v>0.15404786953315339</v>
+        <v>0.147778389480469</v>
       </c>
       <c r="D30">
-        <v>0.2072981438024798</v>
+        <v>0.195417999667521</v>
       </c>
       <c r="E30">
-        <v>0.1953609619732885</v>
+        <v>0.1865370027127148</v>
       </c>
       <c r="F30">
-        <v>0.25411850628529181</v>
+        <v>0.2578919042542825</v>
       </c>
       <c r="G30">
-        <v>0.26085966667022459</v>
+        <v>0.2590709905417387</v>
       </c>
       <c r="H30">
-        <v>0.36893439108699699</v>
+        <v>0.3802942786134272</v>
       </c>
       <c r="I30">
-        <v>0.60775350483287938</v>
+        <v>0.6124978789854471</v>
       </c>
       <c r="J30">
-        <v>0.49961631350766961</v>
+        <v>0.5100035050664894</v>
       </c>
       <c r="K30">
-        <v>0.50733784950900163</v>
+        <v>0.5096379848084002</v>
       </c>
       <c r="L30">
-        <v>0.55075671078383281</v>
+        <v>0.5436397633094953</v>
       </c>
       <c r="M30">
-        <v>0.64617039061353021</v>
+        <v>0.6316518676120157</v>
       </c>
       <c r="N30">
-        <v>0.71950245965892523</v>
+        <v>0.6999205964422911</v>
       </c>
       <c r="O30">
-        <v>0.79776556191158787</v>
+        <v>0.7830821826943373</v>
       </c>
       <c r="P30">
-        <v>0.90859429024849347</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>45</v>
+        <v>0.894906658432096</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B31">
-        <v>7.5607725159523617E-2</v>
+        <v>0.07737038176184441</v>
       </c>
       <c r="C31">
-        <v>0.14708847506007119</v>
+        <v>0.1536156929089882</v>
       </c>
       <c r="D31">
-        <v>0.19064381137374559</v>
+        <v>0.1993376768644302</v>
       </c>
       <c r="E31">
-        <v>0.17902514217341231</v>
+        <v>0.1817555574917581</v>
       </c>
       <c r="F31">
-        <v>0.22831351570419339</v>
+        <v>0.2348279213259654</v>
       </c>
       <c r="G31">
-        <v>0.22578828308966939</v>
+        <v>0.2317595111294339</v>
       </c>
       <c r="H31">
-        <v>0.25856230969692601</v>
+        <v>0.2593564178992169</v>
       </c>
       <c r="I31">
-        <v>0.43927689386514812</v>
+        <v>0.459875195839906</v>
       </c>
       <c r="J31">
-        <v>0.36964400348601412</v>
+        <v>0.3754785819258644</v>
       </c>
       <c r="K31">
-        <v>0.35636176338309378</v>
+        <v>0.3517958060790221</v>
       </c>
       <c r="L31">
-        <v>0.33846812939855442</v>
+        <v>0.3323929231091362</v>
       </c>
       <c r="M31">
-        <v>0.38669118567766553</v>
+        <v>0.3783759343244373</v>
       </c>
       <c r="N31">
-        <v>0.39127740083358142</v>
+        <v>0.3831709942382087</v>
       </c>
       <c r="O31">
-        <v>0.44576036918108303</v>
+        <v>0.4292543326040635</v>
       </c>
       <c r="P31">
-        <v>0.47047509906106327</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>46</v>
+        <v>0.4523595033560238</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
+        </is>
       </c>
       <c r="B32">
-        <v>7.1995181435227207E-2</v>
+        <v>0.07113976980825902</v>
       </c>
       <c r="C32">
-        <v>0.13999553181364049</v>
+        <v>0.1313181084993424</v>
       </c>
       <c r="D32">
-        <v>0.23204169348323311</v>
+        <v>0.2284926266424842</v>
       </c>
       <c r="E32">
-        <v>0.22154720430897951</v>
+        <v>0.2125582493868606</v>
       </c>
       <c r="F32">
-        <v>0.2043387670222129</v>
+        <v>0.2008162056782984</v>
       </c>
       <c r="G32">
-        <v>0.21893826309644021</v>
+        <v>0.2179788691036534</v>
       </c>
       <c r="H32">
-        <v>0.39671361180694648</v>
+        <v>0.3984366198419584</v>
       </c>
       <c r="I32">
-        <v>0.39621825535584099</v>
+        <v>0.397699746954655</v>
       </c>
       <c r="J32">
-        <v>0.37921756084359459</v>
+        <v>0.3857470137800006</v>
       </c>
       <c r="K32">
-        <v>0.35568884455512367</v>
+        <v>0.3612108294753095</v>
       </c>
       <c r="L32">
-        <v>0.34839791245459562</v>
+        <v>0.3465237848538946</v>
       </c>
       <c r="M32">
-        <v>0.34612829464312228</v>
+        <v>0.3435030300022971</v>
       </c>
       <c r="N32">
-        <v>0.38907760161994559</v>
+        <v>0.3746004528909048</v>
       </c>
       <c r="O32">
-        <v>0.42437117439554639</v>
+        <v>0.4168563035671892</v>
       </c>
       <c r="P32">
-        <v>0.46231819447083278</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>47</v>
+        <v>0.4454472926607689</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
+        </is>
       </c>
       <c r="B33">
-        <v>7.4167492444816907E-2</v>
+        <v>0.07291164992198115</v>
       </c>
       <c r="C33">
-        <v>0.14004656549648339</v>
+        <v>0.1363594970330547</v>
       </c>
       <c r="D33">
-        <v>0.236741250952819</v>
+        <v>0.2318248385578143</v>
       </c>
       <c r="E33">
-        <v>0.22073969819864381</v>
+        <v>0.2164387876714761</v>
       </c>
       <c r="F33">
-        <v>0.20371764399313039</v>
+        <v>0.202638075771617</v>
       </c>
       <c r="G33">
-        <v>0.21655288150004531</v>
+        <v>0.2094453963340044</v>
       </c>
       <c r="H33">
-        <v>0.39602244222536909</v>
+        <v>0.380026628230978</v>
       </c>
       <c r="I33">
-        <v>0.38966856980516201</v>
+        <v>0.3778754685460084</v>
       </c>
       <c r="J33">
-        <v>0.37856708620741503</v>
+        <v>0.3700411346476431</v>
       </c>
       <c r="K33">
-        <v>0.33466761609741891</v>
+        <v>0.323270350218912</v>
       </c>
       <c r="L33">
-        <v>0.33087150281882738</v>
+        <v>0.3247536766155174</v>
       </c>
       <c r="M33">
-        <v>0.31821982212547639</v>
+        <v>0.3202848228116953</v>
       </c>
       <c r="N33">
-        <v>0.35746952159992051</v>
+        <v>0.3531826004839733</v>
       </c>
       <c r="O33">
-        <v>0.38589925205223491</v>
+        <v>0.3826042064094257</v>
       </c>
       <c r="P33">
-        <v>0.41602955126803032</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>48</v>
+        <v>0.4069067440229491</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
+        </is>
       </c>
       <c r="B34">
-        <v>7.0906286642716754E-2</v>
+        <v>0.06729292389907943</v>
       </c>
       <c r="C34">
-        <v>0.13574514424303449</v>
+        <v>0.130144977018025</v>
       </c>
       <c r="D34">
-        <v>0.22973934575292609</v>
+        <v>0.2286429120521199</v>
       </c>
       <c r="E34">
-        <v>0.21582322464693951</v>
+        <v>0.2152697402200887</v>
       </c>
       <c r="F34">
-        <v>0.20723665976926769</v>
+        <v>0.1958206735774037</v>
       </c>
       <c r="G34">
-        <v>0.21488352786127929</v>
+        <v>0.2054304411093179</v>
       </c>
       <c r="H34">
-        <v>0.3803784390019892</v>
+        <v>0.3731379758075802</v>
       </c>
       <c r="I34">
-        <v>0.38433962681610229</v>
+        <v>0.3826212451777345</v>
       </c>
       <c r="J34">
-        <v>0.37784244692709551</v>
+        <v>0.3799216517510868</v>
       </c>
       <c r="K34">
-        <v>0.3319683526649278</v>
+        <v>0.3363375890838749</v>
       </c>
       <c r="L34">
-        <v>0.33484424652411271</v>
+        <v>0.3334113508925768</v>
       </c>
       <c r="M34">
-        <v>0.31708076018096498</v>
+        <v>0.3230785178087606</v>
       </c>
       <c r="N34">
-        <v>0.36256030622226271</v>
+        <v>0.3639164966006936</v>
       </c>
       <c r="O34">
-        <v>0.39078544302819129</v>
+        <v>0.3906883148304183</v>
       </c>
       <c r="P34">
-        <v>0.41982402468120189</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>49</v>
+        <v>0.4145929276672172</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
+        </is>
       </c>
       <c r="B35">
-        <v>7.8168567379392526E-2</v>
+        <v>0.07036447400021914</v>
       </c>
       <c r="C35">
-        <v>0.1450429912446039</v>
+        <v>0.1370193552139107</v>
       </c>
       <c r="D35">
-        <v>0.23926367379361541</v>
+        <v>0.2329697309418057</v>
       </c>
       <c r="E35">
-        <v>0.22424231621717411</v>
+        <v>0.2173407358820299</v>
       </c>
       <c r="F35">
-        <v>0.2133689980290806</v>
+        <v>0.2053752854557724</v>
       </c>
       <c r="G35">
-        <v>0.21776082203871869</v>
+        <v>0.2162902393863993</v>
       </c>
       <c r="H35">
-        <v>0.37123925633082228</v>
+        <v>0.3708744471870626</v>
       </c>
       <c r="I35">
-        <v>0.38413566558019541</v>
+        <v>0.390640623115628</v>
       </c>
       <c r="J35">
-        <v>0.39463213771463151</v>
+        <v>0.3961199267927491</v>
       </c>
       <c r="K35">
-        <v>0.33790664470807569</v>
+        <v>0.3470206908936629</v>
       </c>
       <c r="L35">
-        <v>0.34400089017187219</v>
+        <v>0.3471870712000744</v>
       </c>
       <c r="M35">
-        <v>0.33104572059775678</v>
+        <v>0.3333134366057893</v>
       </c>
       <c r="N35">
-        <v>0.36077068029816439</v>
+        <v>0.3618442912181873</v>
       </c>
       <c r="O35">
-        <v>0.39057261388306003</v>
+        <v>0.394430368079889</v>
       </c>
       <c r="P35">
-        <v>0.40194480973892133</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>50</v>
+        <v>0.4021954498267158</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+        </is>
       </c>
       <c r="B36">
-        <v>7.0684246575086845E-2</v>
+        <v>0.07473056995451285</v>
       </c>
       <c r="C36">
-        <v>0.13538572173512711</v>
+        <v>0.1453555661660082</v>
       </c>
       <c r="D36">
-        <v>0.2324378981767746</v>
+        <v>0.2389773942009832</v>
       </c>
       <c r="E36">
-        <v>0.22234095236274501</v>
+        <v>0.2219962896753369</v>
       </c>
       <c r="F36">
-        <v>0.20406731598839031</v>
+        <v>0.2132423582402115</v>
       </c>
       <c r="G36">
-        <v>0.22389720245026881</v>
+        <v>0.229941011046015</v>
       </c>
       <c r="H36">
-        <v>0.41903371159852371</v>
+        <v>0.4357483394134003</v>
       </c>
       <c r="I36">
-        <v>0.4101424267365143</v>
+        <v>0.4169324684827601</v>
       </c>
       <c r="J36">
-        <v>0.39299362118181208</v>
+        <v>0.4044252323491563</v>
       </c>
       <c r="K36">
-        <v>0.36839259186591589</v>
+        <v>0.3678641912861077</v>
       </c>
       <c r="L36">
-        <v>0.360528148334754</v>
+        <v>0.3636656687322286</v>
       </c>
       <c r="M36">
-        <v>0.36516914312176912</v>
+        <v>0.3549039319481156</v>
       </c>
       <c r="N36">
-        <v>0.40647899951918592</v>
+        <v>0.3994495361098796</v>
       </c>
       <c r="O36">
-        <v>0.45425118394549868</v>
+        <v>0.4515160552941564</v>
       </c>
       <c r="P36">
-        <v>0.51376469156560978</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>51</v>
+        <v>0.5089224217314906</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
+        </is>
       </c>
       <c r="B37">
-        <v>6.6910334274210739E-2</v>
+        <v>0.06712372035595536</v>
       </c>
       <c r="C37">
-        <v>0.12995546307879799</v>
+        <v>0.1272070966638671</v>
       </c>
       <c r="D37">
-        <v>0.22560001767655299</v>
+        <v>0.2208118833581633</v>
       </c>
       <c r="E37">
-        <v>0.21530017061204029</v>
+        <v>0.2114662720038407</v>
       </c>
       <c r="F37">
-        <v>0.20166239399532551</v>
+        <v>0.1933223498168176</v>
       </c>
       <c r="G37">
-        <v>0.21235773332150279</v>
+        <v>0.2114115948780261</v>
       </c>
       <c r="H37">
-        <v>0.40746308083982458</v>
+        <v>0.3979938204352149</v>
       </c>
       <c r="I37">
-        <v>0.40188661105636558</v>
+        <v>0.3951815105900816</v>
       </c>
       <c r="J37">
-        <v>0.38680806591450828</v>
+        <v>0.38562907164682</v>
       </c>
       <c r="K37">
-        <v>0.35685411563573921</v>
+        <v>0.3548210150440567</v>
       </c>
       <c r="L37">
-        <v>0.35662746848163418</v>
+        <v>0.3541082907231</v>
       </c>
       <c r="M37">
-        <v>0.34915170142931778</v>
+        <v>0.350011923660455</v>
       </c>
       <c r="N37">
-        <v>0.39897839410742791</v>
+        <v>0.3972751460511406</v>
       </c>
       <c r="O37">
-        <v>0.44188287275028282</v>
+        <v>0.441815262104426</v>
       </c>
       <c r="P37">
-        <v>0.50147505373625689</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>52</v>
+        <v>0.5000301383265465</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
+        </is>
       </c>
       <c r="B38">
-        <v>7.3801927335644751E-2</v>
+        <v>0.07097459395452993</v>
       </c>
       <c r="C38">
-        <v>0.14063093579723671</v>
+        <v>0.1341346374750731</v>
       </c>
       <c r="D38">
-        <v>0.24038380901162759</v>
+        <v>0.2276582597694146</v>
       </c>
       <c r="E38">
-        <v>0.2213718247595842</v>
+        <v>0.2080613621289629</v>
       </c>
       <c r="F38">
-        <v>0.20729454198602831</v>
+        <v>0.1940232340712603</v>
       </c>
       <c r="G38">
-        <v>0.21782386619567001</v>
+        <v>0.2046894891542714</v>
       </c>
       <c r="H38">
-        <v>0.39966576078240362</v>
+        <v>0.3786249718048764</v>
       </c>
       <c r="I38">
-        <v>0.38701467680610002</v>
+        <v>0.380882842692014</v>
       </c>
       <c r="J38">
-        <v>0.37765370114345448</v>
+        <v>0.3697840949454634</v>
       </c>
       <c r="K38">
-        <v>0.35513496928045019</v>
+        <v>0.3495308207269469</v>
       </c>
       <c r="L38">
-        <v>0.35244927084462668</v>
+        <v>0.3489075195046838</v>
       </c>
       <c r="M38">
-        <v>0.34630533580616002</v>
+        <v>0.3467535350346005</v>
       </c>
       <c r="N38">
-        <v>0.39070445967312878</v>
+        <v>0.3840979831199923</v>
       </c>
       <c r="O38">
-        <v>0.43170234719041578</v>
+        <v>0.4135188558521128</v>
       </c>
       <c r="P38">
-        <v>0.47651475445729718</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>53</v>
+        <v>0.469317506313921</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B39">
-        <v>7.150877380156262E-2</v>
+        <v>0.07312781216885915</v>
       </c>
       <c r="C39">
-        <v>0.1383612960744024</v>
+        <v>0.1385980379417396</v>
       </c>
       <c r="D39">
-        <v>0.2382706426261868</v>
+        <v>0.2324817490564553</v>
       </c>
       <c r="E39">
-        <v>0.2231278187937509</v>
+        <v>0.219800650824664</v>
       </c>
       <c r="F39">
-        <v>0.21139930803565571</v>
+        <v>0.2005136844959313</v>
       </c>
       <c r="G39">
-        <v>0.22069496467831301</v>
+        <v>0.2159977120725463</v>
       </c>
       <c r="H39">
-        <v>0.40312666252582541</v>
+        <v>0.392024672819816</v>
       </c>
       <c r="I39">
-        <v>0.39699670554580951</v>
+        <v>0.3886624145198087</v>
       </c>
       <c r="J39">
-        <v>0.3919441242608222</v>
+        <v>0.3761863467946833</v>
       </c>
       <c r="K39">
-        <v>0.36932060375624698</v>
+        <v>0.3512552044744585</v>
       </c>
       <c r="L39">
-        <v>0.36449432421354439</v>
+        <v>0.3550666734474831</v>
       </c>
       <c r="M39">
-        <v>0.35953888437241038</v>
+        <v>0.3453046994587969</v>
       </c>
       <c r="N39">
-        <v>0.3883228337746959</v>
+        <v>0.3827495199269257</v>
       </c>
       <c r="O39">
-        <v>0.42156281146919988</v>
+        <v>0.4166101122363515</v>
       </c>
       <c r="P39">
-        <v>0.45949719779872028</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>54</v>
+        <v>0.4619329923383294</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+        </is>
       </c>
       <c r="B40">
-        <v>7.1246700151228928E-2</v>
+        <v>0.07259329892980512</v>
       </c>
       <c r="C40">
-        <v>0.13979616828587921</v>
+        <v>0.1345921176015184</v>
       </c>
       <c r="D40">
-        <v>0.23538584370792109</v>
+        <v>0.2249689760872991</v>
       </c>
       <c r="E40">
-        <v>0.21891724539756521</v>
+        <v>0.210736283312182</v>
       </c>
       <c r="F40">
-        <v>0.20359566526071321</v>
+        <v>0.1988677515589792</v>
       </c>
       <c r="G40">
-        <v>0.2096641850149957</v>
+        <v>0.2101804318076824</v>
       </c>
       <c r="H40">
-        <v>0.34827920116990302</v>
+        <v>0.3568091301924503</v>
       </c>
       <c r="I40">
-        <v>0.36410328104438039</v>
+        <v>0.3678346252986001</v>
       </c>
       <c r="J40">
-        <v>0.36578836161797029</v>
+        <v>0.3650958239194347</v>
       </c>
       <c r="K40">
-        <v>0.31959747594907773</v>
+        <v>0.3101493435757403</v>
       </c>
       <c r="L40">
-        <v>0.33190228945069539</v>
+        <v>0.3245309266150815</v>
       </c>
       <c r="M40">
-        <v>0.33868886188899949</v>
+        <v>0.3207938442842878</v>
       </c>
       <c r="N40">
-        <v>0.36249163841162341</v>
+        <v>0.3450453601060306</v>
       </c>
       <c r="O40">
-        <v>0.38793406457663149</v>
+        <v>0.3775586785898598</v>
       </c>
       <c r="P40">
-        <v>0.4019126141042087</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>55</v>
+        <v>0.3885501509409019</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B41">
-        <v>0.14815827740035839</v>
+        <v>0.1490655056232214</v>
       </c>
       <c r="C41">
-        <v>0.32516363901309031</v>
+        <v>0.3365963060440381</v>
       </c>
       <c r="D41">
-        <v>0.28299933922697562</v>
+        <v>0.2970372341995525</v>
       </c>
       <c r="E41">
-        <v>0.32111822939922868</v>
+        <v>0.3247669300079282</v>
       </c>
       <c r="F41">
-        <v>0.52291562474265052</v>
+        <v>0.529167099466423</v>
       </c>
       <c r="G41">
-        <v>0.55201698526728127</v>
+        <v>0.5595924198457294</v>
       </c>
       <c r="H41">
-        <v>0.5554404383963949</v>
+        <v>0.5705356289432368</v>
       </c>
       <c r="I41">
-        <v>0.55451094140983426</v>
+        <v>0.5652848001488244</v>
       </c>
       <c r="J41">
-        <v>0.59984022537764559</v>
+        <v>0.6047920620891054</v>
       </c>
       <c r="K41">
-        <v>0.66239865047900404</v>
+        <v>0.6569646051951774</v>
       </c>
       <c r="L41">
-        <v>0.71320455979868014</v>
+        <v>0.7122697319011305</v>
       </c>
       <c r="M41">
-        <v>0.78886814014374973</v>
+        <v>0.7821650892338847</v>
       </c>
       <c r="N41">
-        <v>0.79417632802139526</v>
+        <v>0.7906385226784745</v>
       </c>
       <c r="O41">
-        <v>0.81251870899758893</v>
+        <v>0.8058037141067246</v>
       </c>
       <c r="P41">
-        <v>0.82507049178823799</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>56</v>
+        <v>0.8168459668839667</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
+        </is>
       </c>
       <c r="B42">
-        <v>9.7660723948482159E-2</v>
+        <v>0.09514104987411134</v>
       </c>
       <c r="C42">
-        <v>0.25233157488214081</v>
+        <v>0.2447027264272519</v>
       </c>
       <c r="D42">
-        <v>0.2545733080737364</v>
+        <v>0.2467679860347173</v>
       </c>
       <c r="E42">
-        <v>0.2875055467663612</v>
+        <v>0.275373966014446</v>
       </c>
       <c r="F42">
-        <v>0.46648125261366391</v>
+        <v>0.458349144077238</v>
       </c>
       <c r="G42">
-        <v>0.36098303127919612</v>
+        <v>0.3594137291615068</v>
       </c>
       <c r="H42">
-        <v>0.26639136809376479</v>
+        <v>0.2799617608452066</v>
       </c>
       <c r="I42">
-        <v>0.32579888457418982</v>
+        <v>0.3318537540065947</v>
       </c>
       <c r="J42">
-        <v>0.39961354807741623</v>
+        <v>0.4038340993871228</v>
       </c>
       <c r="K42">
-        <v>0.47139547386128328</v>
+        <v>0.4780321290321683</v>
       </c>
       <c r="L42">
-        <v>0.51810939454781413</v>
+        <v>0.5281896288282524</v>
       </c>
       <c r="M42">
-        <v>0.56413807465634647</v>
+        <v>0.5710940168667763</v>
       </c>
       <c r="N42">
-        <v>0.59140633238632279</v>
+        <v>0.6073802445048522</v>
       </c>
       <c r="O42">
-        <v>0.6139740554802382</v>
+        <v>0.6281179758646911</v>
       </c>
       <c r="P42">
-        <v>0.62788490853474299</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>57</v>
+        <v>0.639330596537326</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+        </is>
       </c>
       <c r="B43">
-        <v>9.4213752516097801E-2</v>
+        <v>0.09822444421045941</v>
       </c>
       <c r="C43">
-        <v>0.2292356083505159</v>
+        <v>0.2271004104326129</v>
       </c>
       <c r="D43">
-        <v>0.22203017013221071</v>
+        <v>0.2171616570198887</v>
       </c>
       <c r="E43">
-        <v>0.21706479392622449</v>
+        <v>0.2235192977387298</v>
       </c>
       <c r="F43">
-        <v>0.34494375721018788</v>
+        <v>0.3460470624203867</v>
       </c>
       <c r="G43">
-        <v>0.28271731818733831</v>
+        <v>0.2839446117292472</v>
       </c>
       <c r="H43">
-        <v>0.2584789564020572</v>
+        <v>0.2584892996416457</v>
       </c>
       <c r="I43">
-        <v>0.30688606098349852</v>
+        <v>0.3064118626029328</v>
       </c>
       <c r="J43">
-        <v>0.35390790885726831</v>
+        <v>0.3584702385853312</v>
       </c>
       <c r="K43">
-        <v>0.37714080051913668</v>
+        <v>0.3875597346435118</v>
       </c>
       <c r="L43">
-        <v>0.43628439365746391</v>
+        <v>0.4343642889962925</v>
       </c>
       <c r="M43">
-        <v>0.43842184100221171</v>
+        <v>0.4449166534126942</v>
       </c>
       <c r="N43">
-        <v>0.50324548032729055</v>
+        <v>0.5026029824828034</v>
       </c>
       <c r="O43">
-        <v>0.55582071584704129</v>
+        <v>0.5549912584818245</v>
       </c>
       <c r="P43">
-        <v>0.59501239504910475</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>58</v>
+        <v>0.5851018650879896</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
+        </is>
       </c>
       <c r="B44">
-        <v>0.14066009976491789</v>
+        <v>0.1429191901859555</v>
       </c>
       <c r="C44">
-        <v>0.13380456166095811</v>
+        <v>0.1382917768582792</v>
       </c>
       <c r="D44">
-        <v>0.19616677056514581</v>
+        <v>0.1978290497321425</v>
       </c>
       <c r="E44">
-        <v>0.2676430874937471</v>
+        <v>0.2684406729439897</v>
       </c>
       <c r="F44">
-        <v>0.36447226776952169</v>
+        <v>0.3693640016875882</v>
       </c>
       <c r="G44">
-        <v>0.38599786219165938</v>
+        <v>0.3740444685379318</v>
       </c>
       <c r="H44">
-        <v>0.45057691416444601</v>
+        <v>0.4506567953429677</v>
       </c>
       <c r="I44">
-        <v>0.54536574496431689</v>
+        <v>0.5476639537084135</v>
       </c>
       <c r="J44">
-        <v>0.61302276358953434</v>
+        <v>0.6118992102428737</v>
       </c>
       <c r="K44">
-        <v>0.62427535931713196</v>
+        <v>0.6259271816037338</v>
       </c>
       <c r="L44">
-        <v>0.65481975942484438</v>
+        <v>0.6581714211141718</v>
       </c>
       <c r="M44">
-        <v>0.66097797901557365</v>
+        <v>0.66506838332847</v>
       </c>
       <c r="N44">
-        <v>0.7028596301036214</v>
+        <v>0.7042118087948532</v>
       </c>
       <c r="O44">
-        <v>0.7528470710363413</v>
+        <v>0.7502404264802121</v>
       </c>
       <c r="P44">
-        <v>0.8337807050916739</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>59</v>
+        <v>0.8240497012345667</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>adj_snv_sder_c(1,3,5)_</t>
+        </is>
       </c>
       <c r="B45">
-        <v>0.1681786137934182</v>
+        <v>0.1705025651057054</v>
       </c>
       <c r="C45">
-        <v>0.49395242537340778</v>
+        <v>0.5079261556435934</v>
       </c>
       <c r="D45">
-        <v>0.48894696437298613</v>
+        <v>0.497343947703733</v>
       </c>
       <c r="E45">
-        <v>0.58407254467066361</v>
+        <v>0.5828731884114323</v>
       </c>
       <c r="F45">
-        <v>0.61783182645890644</v>
+        <v>0.6204915893506291</v>
       </c>
       <c r="G45">
-        <v>0.64734761547752162</v>
+        <v>0.6480264947355574</v>
       </c>
       <c r="H45">
-        <v>0.68977078706007788</v>
+        <v>0.6930919175501906</v>
       </c>
       <c r="I45">
-        <v>0.69281649026412795</v>
+        <v>0.696536154166538</v>
       </c>
       <c r="J45">
-        <v>0.76053544198002021</v>
+        <v>0.7560593751624463</v>
       </c>
       <c r="K45">
-        <v>0.82019235519121203</v>
+        <v>0.8206776079059649</v>
       </c>
       <c r="L45">
-        <v>0.86263461817265774</v>
+        <v>0.851836769212291</v>
       </c>
       <c r="M45">
-        <v>0.92155682578913034</v>
+        <v>0.9130858772949259</v>
       </c>
       <c r="N45">
-        <v>1.000528753028717</v>
+        <v>0.992293503755272</v>
       </c>
       <c r="O45">
-        <v>1.029234594475219</v>
+        <v>1.022746503372373</v>
       </c>
       <c r="P45">
-        <v>1.063425625518817</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>60</v>
+        <v>1.063017939789391</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>adj_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B46">
-        <v>5.7024109743938331E-2</v>
+        <v>0.05785073043397997</v>
       </c>
       <c r="C46">
-        <v>0.60367416097651283</v>
+        <v>0.6065384398387017</v>
       </c>
       <c r="D46">
-        <v>0.53148689394168436</v>
+        <v>0.5337321706532547</v>
       </c>
       <c r="E46">
-        <v>0.42508814098898062</v>
+        <v>0.4140207501100426</v>
       </c>
       <c r="F46">
-        <v>0.41912099950300269</v>
+        <v>0.4127102312907328</v>
       </c>
       <c r="G46">
-        <v>0.4380567623992811</v>
+        <v>0.4422624187651038</v>
       </c>
       <c r="H46">
-        <v>0.4193894438351663</v>
+        <v>0.4175135219742114</v>
       </c>
       <c r="I46">
-        <v>0.45048610883494422</v>
+        <v>0.4461747467248345</v>
       </c>
       <c r="J46">
-        <v>0.4898990547730252</v>
+        <v>0.492627000213079</v>
       </c>
       <c r="K46">
-        <v>0.50494840164316124</v>
+        <v>0.5121428708115359</v>
       </c>
       <c r="L46">
-        <v>0.53490015873757502</v>
+        <v>0.5452009976370192</v>
       </c>
       <c r="M46">
-        <v>0.59883492757550594</v>
+        <v>0.6095662719269517</v>
       </c>
       <c r="N46">
-        <v>0.62497810898456641</v>
+        <v>0.6370916423769</v>
       </c>
       <c r="O46">
-        <v>0.64062449633481366</v>
+        <v>0.6503788765778507</v>
       </c>
       <c r="P46">
-        <v>0.68023675843830755</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>61</v>
+        <v>0.691939455675543</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
+        </is>
       </c>
       <c r="B47">
-        <v>9.7840702018259271E-2</v>
+        <v>0.110541872057105</v>
       </c>
       <c r="C47">
-        <v>0.2355762573987942</v>
+        <v>0.2505289486349514</v>
       </c>
       <c r="D47">
-        <v>0.37379025137952132</v>
+        <v>0.3843532461328639</v>
       </c>
       <c r="E47">
-        <v>0.44847416601942092</v>
+        <v>0.4660579052871431</v>
       </c>
       <c r="F47">
-        <v>0.36088606970708442</v>
+        <v>0.3608401355829366</v>
       </c>
       <c r="G47">
-        <v>0.35957629853215178</v>
+        <v>0.3679600456349216</v>
       </c>
       <c r="H47">
-        <v>0.39819405247843331</v>
+        <v>0.3983615024108103</v>
       </c>
       <c r="I47">
-        <v>0.44150195029650169</v>
+        <v>0.4492293443922828</v>
       </c>
       <c r="J47">
-        <v>0.53840403192282282</v>
+        <v>0.5439030485689029</v>
       </c>
       <c r="K47">
-        <v>0.54566799587032988</v>
+        <v>0.5503002294094868</v>
       </c>
       <c r="L47">
-        <v>0.56821469300490579</v>
+        <v>0.5779980109062858</v>
       </c>
       <c r="M47">
-        <v>0.59317112657457194</v>
+        <v>0.6056296989672674</v>
       </c>
       <c r="N47">
-        <v>0.63495831259740754</v>
+        <v>0.6486172670868847</v>
       </c>
       <c r="O47">
-        <v>0.66950679618122455</v>
+        <v>0.6798944894643668</v>
       </c>
       <c r="P47">
-        <v>0.70330666548565879</v>
+        <v>0.7187812332221583</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:P18 B20:P47 B19:K19 M19:P19">
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="greaterThan">
-      <formula>0.2</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="lessThan">
-      <formula>0.2</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/ROSA_vitaSPEC/Results/test_pretraitements/ratio.beta.natif/Resultats_ratio.beta.natif_moy_diff.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/ratio.beta.natif/Resultats_ratio.beta.natif_moy_diff.xlsx
@@ -1,21 +1,205 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U108-N806\Documents\STAGE_M2_ROSA_NIRS\VitaSPEC\vitaspec_R\ROSA_vitaSPEC\Results\test_pretraitements\ratio.beta.natif\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+  <si>
+    <t>Pretraitement</t>
+  </si>
+  <si>
+    <t>LV1_diff</t>
+  </si>
+  <si>
+    <t>LV2_diff</t>
+  </si>
+  <si>
+    <t>LV3_diff</t>
+  </si>
+  <si>
+    <t>LV4_diff</t>
+  </si>
+  <si>
+    <t>LV5_diff</t>
+  </si>
+  <si>
+    <t>LV6_diff</t>
+  </si>
+  <si>
+    <t>LV7_diff</t>
+  </si>
+  <si>
+    <t>LV8_diff</t>
+  </si>
+  <si>
+    <t>LV9_diff</t>
+  </si>
+  <si>
+    <t>LV10_diff</t>
+  </si>
+  <si>
+    <t>LV11_diff</t>
+  </si>
+  <si>
+    <t>LV12_diff</t>
+  </si>
+  <si>
+    <t>LV13_diff</t>
+  </si>
+  <si>
+    <t>LV14_diff</t>
+  </si>
+  <si>
+    <t>LV15_diff</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1000,1)_snv_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_msc_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_snv_sder_c(1,3,5)_</t>
+  </si>
+  <si>
+    <t>adj_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -61,13 +245,52 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -109,7 +332,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -141,9 +364,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -175,6 +399,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -350,2485 +575,2173 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P47"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:P43"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="51.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="16" width="12" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Pretraitement</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>LV1_diff</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>LV2_diff</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>LV3_diff</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>LV4_diff</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>LV5_diff</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>LV6_diff</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>LV7_diff</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>LV8_diff</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>LV9_diff</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>LV10_diff</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>LV11_diff</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>LV12_diff</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>LV13_diff</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>LV14_diff</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>LV15_diff</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1000,1)_snv_</t>
-        </is>
+    <row r="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>16</v>
       </c>
       <c r="B2">
-        <v>0.05563109121187666</v>
+        <v>5.5273494550734208E-2</v>
       </c>
       <c r="C2">
-        <v>0.1141681418988816</v>
+        <v>0.11699703020209409</v>
       </c>
       <c r="D2">
-        <v>0.1350444710473837</v>
+        <v>0.13272378875004279</v>
       </c>
       <c r="E2">
-        <v>0.1349674012921784</v>
+        <v>0.1300749895247697</v>
       </c>
       <c r="F2">
-        <v>0.1884064406164</v>
+        <v>0.1883708066053518</v>
       </c>
       <c r="G2">
-        <v>0.2713196956808722</v>
+        <v>0.26453852984634019</v>
       </c>
       <c r="H2">
-        <v>0.2592310812832138</v>
+        <v>0.25470509926722867</v>
       </c>
       <c r="I2">
-        <v>0.2956790093407657</v>
+        <v>0.2927526184168005</v>
       </c>
       <c r="J2">
-        <v>0.38866178134463</v>
+        <v>0.37648122516372889</v>
       </c>
       <c r="K2">
-        <v>0.3838680453386865</v>
+        <v>0.37222252709756148</v>
       </c>
       <c r="L2">
-        <v>0.4192172857718994</v>
+        <v>0.40904284152108561</v>
       </c>
       <c r="M2">
-        <v>0.448640543181819</v>
+        <v>0.44407892220993211</v>
       </c>
       <c r="N2">
-        <v>0.438823116296888</v>
+        <v>0.43741960194427759</v>
       </c>
       <c r="O2">
-        <v>0.4247954252031472</v>
+        <v>0.41859501659976789</v>
       </c>
       <c r="P2">
-        <v>0.4087701776484949</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>0.40633617487430468</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>17</v>
       </c>
       <c r="B3">
-        <v>0.05690719771576779</v>
+        <v>5.8722899276375452E-2</v>
       </c>
       <c r="C3">
-        <v>0.3656741634320529</v>
+        <v>0.37310080799210421</v>
       </c>
       <c r="D3">
-        <v>0.4344263395684268</v>
+        <v>0.44404777802975709</v>
       </c>
       <c r="E3">
-        <v>0.3389676181624751</v>
+        <v>0.34177923843633368</v>
       </c>
       <c r="F3">
-        <v>0.3329328258166036</v>
+        <v>0.33046896000685838</v>
       </c>
       <c r="G3">
-        <v>0.3452363838127659</v>
+        <v>0.34796933603627461</v>
       </c>
       <c r="H3">
-        <v>0.3828228131874102</v>
+        <v>0.38530516015267408</v>
       </c>
       <c r="I3">
-        <v>0.413622321528216</v>
+        <v>0.41100115827036549</v>
       </c>
       <c r="J3">
-        <v>0.4145014783204052</v>
+        <v>0.41054298913569609</v>
       </c>
       <c r="K3">
-        <v>0.4224512782347168</v>
+        <v>0.42104977162767149</v>
       </c>
       <c r="L3">
-        <v>0.451740142258661</v>
+        <v>0.45363472094945417</v>
       </c>
       <c r="M3">
-        <v>0.491842887049267</v>
+        <v>0.49657292737703379</v>
       </c>
       <c r="N3">
-        <v>0.5551326739648299</v>
+        <v>0.55329261888215997</v>
       </c>
       <c r="O3">
-        <v>0.6050636996151983</v>
+        <v>0.60846779209101742</v>
       </c>
       <c r="P3">
-        <v>0.6049074430458261</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_msc_</t>
-        </is>
+        <v>0.60449642399546155</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>18</v>
       </c>
       <c r="B4">
-        <v>0.04494218362072765</v>
+        <v>4.7458373040784027E-2</v>
       </c>
       <c r="C4">
-        <v>0.06688501103216773</v>
+        <v>7.3477954549826391E-2</v>
       </c>
       <c r="D4">
-        <v>0.1659928894240691</v>
+        <v>0.17114380046366551</v>
       </c>
       <c r="E4">
-        <v>0.1783569362423504</v>
+        <v>0.19520276951655299</v>
       </c>
       <c r="F4">
-        <v>0.3420239290087846</v>
+        <v>0.36136417662623288</v>
       </c>
       <c r="G4">
-        <v>0.3166177519659898</v>
+        <v>0.31511034762772522</v>
       </c>
       <c r="H4">
-        <v>0.285640315202581</v>
+        <v>0.29854554458524901</v>
       </c>
       <c r="I4">
-        <v>0.3525720787937666</v>
+        <v>0.3662827473118811</v>
       </c>
       <c r="J4">
-        <v>0.4000416086038757</v>
+        <v>0.40404754181787839</v>
       </c>
       <c r="K4">
-        <v>0.4349110002657984</v>
+        <v>0.43856138488319768</v>
       </c>
       <c r="L4">
-        <v>0.4424470332483901</v>
+        <v>0.44596655585463441</v>
       </c>
       <c r="M4">
-        <v>0.4372287183384281</v>
+        <v>0.44666608089371662</v>
       </c>
       <c r="N4">
-        <v>0.4407208696816092</v>
+        <v>0.44649203342045168</v>
       </c>
       <c r="O4">
-        <v>0.4540594255382683</v>
+        <v>0.46296182386461421</v>
       </c>
       <c r="P4">
-        <v>0.4903302276268759</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
-        </is>
+        <v>0.49939485793758442</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>19</v>
       </c>
       <c r="B5">
-        <v>0.04254617768974436</v>
+        <v>4.5620027108750107E-2</v>
       </c>
       <c r="C5">
-        <v>0.1699115880435274</v>
+        <v>0.1653716925063764</v>
       </c>
       <c r="D5">
-        <v>0.2071950525689915</v>
+        <v>0.20645670746670411</v>
       </c>
       <c r="E5">
-        <v>0.4538816264250832</v>
+        <v>0.44738099349115862</v>
       </c>
       <c r="F5">
-        <v>0.3262911013825802</v>
+        <v>0.32477411893704611</v>
       </c>
       <c r="G5">
-        <v>0.383236599051708</v>
+        <v>0.38777277427532558</v>
       </c>
       <c r="H5">
-        <v>0.3972745928875171</v>
+        <v>0.38564779976073138</v>
       </c>
       <c r="I5">
-        <v>0.3945531675737108</v>
+        <v>0.38486879094738158</v>
       </c>
       <c r="J5">
-        <v>0.356258973089829</v>
+        <v>0.34865721529382648</v>
       </c>
       <c r="K5">
-        <v>0.3555555621927972</v>
+        <v>0.35040418265424711</v>
       </c>
       <c r="L5">
-        <v>0.3702601460736326</v>
+        <v>0.36141962262739669</v>
       </c>
       <c r="M5">
-        <v>0.3944217102994211</v>
+        <v>0.38067705771588822</v>
       </c>
       <c r="N5">
-        <v>0.4473828481461685</v>
+        <v>0.43204468338792412</v>
       </c>
       <c r="O5">
-        <v>0.4849359986018651</v>
+        <v>0.46367354216923679</v>
       </c>
       <c r="P5">
-        <v>0.5325513475458845</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
-        </is>
+        <v>0.51187871392204998</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>20</v>
       </c>
       <c r="B6">
-        <v>0.04764650509638865</v>
+        <v>4.4588323447701382E-2</v>
       </c>
       <c r="C6">
-        <v>0.183207882631748</v>
+        <v>0.18558805468668571</v>
       </c>
       <c r="D6">
-        <v>0.1866297060390134</v>
+        <v>0.19301664935590779</v>
       </c>
       <c r="E6">
-        <v>0.4429769980657506</v>
+        <v>0.45039146828596899</v>
       </c>
       <c r="F6">
-        <v>0.2842376428696332</v>
+        <v>0.29903687268441809</v>
       </c>
       <c r="G6">
-        <v>0.3224976662723963</v>
+        <v>0.32869166416003331</v>
       </c>
       <c r="H6">
-        <v>0.3192029394550447</v>
+        <v>0.3311663385883048</v>
       </c>
       <c r="I6">
-        <v>0.2792322794247859</v>
+        <v>0.28040293017795392</v>
       </c>
       <c r="J6">
-        <v>0.2807275689283295</v>
+        <v>0.2852229343484996</v>
       </c>
       <c r="K6">
-        <v>0.2906071650731398</v>
+        <v>0.29969203879129569</v>
       </c>
       <c r="L6">
-        <v>0.3118124417371679</v>
+        <v>0.32087366220576102</v>
       </c>
       <c r="M6">
-        <v>0.3383141829451911</v>
+        <v>0.33968803066751702</v>
       </c>
       <c r="N6">
-        <v>0.3699205888630996</v>
+        <v>0.37300441934802758</v>
       </c>
       <c r="O6">
-        <v>0.3839209928119193</v>
+        <v>0.38383100058182629</v>
       </c>
       <c r="P6">
-        <v>0.4290510674750353</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_</t>
-        </is>
+        <v>0.43121112349880097</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>21</v>
       </c>
       <c r="B7">
-        <v>0.05129048607482588</v>
+        <v>4.8430520453452142E-2</v>
       </c>
       <c r="C7">
-        <v>0.08026916604620876</v>
+        <v>7.6222696096395121E-2</v>
       </c>
       <c r="D7">
-        <v>0.1622380121116061</v>
+        <v>0.1575904991744792</v>
       </c>
       <c r="E7">
-        <v>0.2048776581127008</v>
+        <v>0.1994063778723458</v>
       </c>
       <c r="F7">
-        <v>0.3265856479808825</v>
+        <v>0.32900173330767718</v>
       </c>
       <c r="G7">
-        <v>0.3756123723689413</v>
+        <v>0.36862453900132502</v>
       </c>
       <c r="H7">
-        <v>0.3348907868581779</v>
+        <v>0.33909245358080498</v>
       </c>
       <c r="I7">
-        <v>0.3017558244949132</v>
+        <v>0.30017965073676961</v>
       </c>
       <c r="J7">
-        <v>0.3701208929894783</v>
+        <v>0.37037395702080822</v>
       </c>
       <c r="K7">
-        <v>0.4095258209927923</v>
+        <v>0.41444729235649258</v>
       </c>
       <c r="L7">
-        <v>0.4476402903214154</v>
+        <v>0.43662093085085257</v>
       </c>
       <c r="M7">
-        <v>0.4678828626805808</v>
+        <v>0.46102764350693171</v>
       </c>
       <c r="N7">
-        <v>0.4359159498800375</v>
+        <v>0.4212156969565542</v>
       </c>
       <c r="O7">
-        <v>0.4430143221153206</v>
+        <v>0.43356512622625393</v>
       </c>
       <c r="P7">
-        <v>0.4633799388125083</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
-        </is>
+        <v>0.4549422286385274</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>22</v>
       </c>
       <c r="B8">
-        <v>0.04470175764369676</v>
+        <v>4.575884647518233E-2</v>
       </c>
       <c r="C8">
-        <v>0.07694034708910522</v>
+        <v>7.9736681869914353E-2</v>
       </c>
       <c r="D8">
-        <v>0.174302974153233</v>
+        <v>0.1786533514223145</v>
       </c>
       <c r="E8">
-        <v>0.3311319338950985</v>
+        <v>0.34287884531737062</v>
       </c>
       <c r="F8">
-        <v>0.3175909284541064</v>
+        <v>0.32786490989731137</v>
       </c>
       <c r="G8">
-        <v>0.289680779771142</v>
+        <v>0.29712767939905199</v>
       </c>
       <c r="H8">
-        <v>0.3288111436757097</v>
+        <v>0.33356671527810999</v>
       </c>
       <c r="I8">
-        <v>0.34775625689759</v>
+        <v>0.35131955414945443</v>
       </c>
       <c r="J8">
-        <v>0.3606248465013536</v>
+        <v>0.35635315727199679</v>
       </c>
       <c r="K8">
-        <v>0.3772489238440932</v>
+        <v>0.37760617782942468</v>
       </c>
       <c r="L8">
-        <v>0.3966809285322583</v>
+        <v>0.40035079358568221</v>
       </c>
       <c r="M8">
-        <v>0.3934641598669181</v>
+        <v>0.40092417498981409</v>
       </c>
       <c r="N8">
-        <v>0.3885272226696632</v>
+        <v>0.39605531953452611</v>
       </c>
       <c r="O8">
-        <v>0.4049596406593578</v>
+        <v>0.41284474291346063</v>
       </c>
       <c r="P8">
-        <v>0.4399850292092309</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
-        </is>
+        <v>0.44263557280746191</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>23</v>
       </c>
       <c r="B9">
-        <v>0.03913827910869513</v>
+        <v>4.235133642966752E-2</v>
       </c>
       <c r="C9">
-        <v>0.07235782064911446</v>
+        <v>6.9258925326993584E-2</v>
       </c>
       <c r="D9">
-        <v>0.1636434530230358</v>
+        <v>0.16063182381914881</v>
       </c>
       <c r="E9">
-        <v>0.2864773018512722</v>
+        <v>0.29046209591590821</v>
       </c>
       <c r="F9">
-        <v>0.2830164762182684</v>
+        <v>0.2866851332329583</v>
       </c>
       <c r="G9">
-        <v>0.2420818136605644</v>
+        <v>0.24723291487233839</v>
       </c>
       <c r="H9">
-        <v>0.2683509765283728</v>
+        <v>0.27649141682059297</v>
       </c>
       <c r="I9">
-        <v>0.2722841378063341</v>
+        <v>0.27839814017885739</v>
       </c>
       <c r="J9">
-        <v>0.2756746887423166</v>
+        <v>0.28281061502745503</v>
       </c>
       <c r="K9">
-        <v>0.2809646024966752</v>
+        <v>0.28643583739681922</v>
       </c>
       <c r="L9">
-        <v>0.3167418973636862</v>
+        <v>0.32662150854415861</v>
       </c>
       <c r="M9">
-        <v>0.288820648432105</v>
+        <v>0.29743245249426731</v>
       </c>
       <c r="N9">
-        <v>0.2908494111471227</v>
+        <v>0.3003448790068633</v>
       </c>
       <c r="O9">
-        <v>0.3076989625299664</v>
+        <v>0.31438728717025521</v>
       </c>
       <c r="P9">
-        <v>0.3277006448445594</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
-        </is>
+        <v>0.33525565260509033</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>24</v>
       </c>
       <c r="B10">
-        <v>0.04742784847370694</v>
+        <v>4.4845886958435978E-2</v>
       </c>
       <c r="C10">
-        <v>0.07592970546860947</v>
+        <v>7.9299623164726052E-2</v>
       </c>
       <c r="D10">
-        <v>0.1655611608253206</v>
+        <v>0.16855630040655439</v>
       </c>
       <c r="E10">
-        <v>0.2965147460019969</v>
+        <v>0.29281770834914211</v>
       </c>
       <c r="F10">
-        <v>0.28863988315657</v>
+        <v>0.2872407265642784</v>
       </c>
       <c r="G10">
-        <v>0.2536556769020608</v>
+        <v>0.24527039786265839</v>
       </c>
       <c r="H10">
-        <v>0.2717997133197904</v>
+        <v>0.27223244136688529</v>
       </c>
       <c r="I10">
-        <v>0.2793942038953021</v>
+        <v>0.27337509257797249</v>
       </c>
       <c r="J10">
-        <v>0.2858822708258912</v>
+        <v>0.27151693445203068</v>
       </c>
       <c r="K10">
-        <v>0.2752615182132013</v>
+        <v>0.27652545204019169</v>
       </c>
       <c r="L10">
-        <v>0.3264273006355159</v>
+        <v>0.32141443397628378</v>
       </c>
       <c r="M10">
-        <v>0.2950863847206216</v>
+        <v>0.29152623762569252</v>
       </c>
       <c r="N10">
-        <v>0.2905058778256568</v>
+        <v>0.29348198062837427</v>
       </c>
       <c r="O10">
-        <v>0.3117439654784731</v>
+        <v>0.31394290497645999</v>
       </c>
       <c r="P10">
-        <v>0.3274816490644545</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-        </is>
+        <v>0.33678664956727228</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>25</v>
       </c>
       <c r="B11">
-        <v>0.04276718134545312</v>
+        <v>4.17565939156068E-2</v>
       </c>
       <c r="C11">
-        <v>0.07648880988659193</v>
+        <v>7.4607989883231196E-2</v>
       </c>
       <c r="D11">
-        <v>0.1720536324294984</v>
+        <v>0.16443678060174849</v>
       </c>
       <c r="E11">
-        <v>0.3049550503545099</v>
+        <v>0.2913979225460786</v>
       </c>
       <c r="F11">
-        <v>0.296933152773956</v>
+        <v>0.28511040850676378</v>
       </c>
       <c r="G11">
-        <v>0.247366030912389</v>
+        <v>0.2459225466870012</v>
       </c>
       <c r="H11">
-        <v>0.2831893855415533</v>
+        <v>0.28082860042638769</v>
       </c>
       <c r="I11">
-        <v>0.2798800743463626</v>
+        <v>0.28675404053673642</v>
       </c>
       <c r="J11">
-        <v>0.2855788937798672</v>
+        <v>0.29834247628636029</v>
       </c>
       <c r="K11">
-        <v>0.2809568941021483</v>
+        <v>0.29473992957109718</v>
       </c>
       <c r="L11">
-        <v>0.3117011848275794</v>
+        <v>0.32455316659682348</v>
       </c>
       <c r="M11">
-        <v>0.2921491830835295</v>
+        <v>0.30027780166632051</v>
       </c>
       <c r="N11">
-        <v>0.292696306757753</v>
+        <v>0.29537821649178481</v>
       </c>
       <c r="O11">
-        <v>0.3147100788722638</v>
+        <v>0.32096414112163008</v>
       </c>
       <c r="P11">
-        <v>0.32881059973584</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
-        </is>
+        <v>0.33275838287263432</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>26</v>
       </c>
       <c r="B12">
-        <v>0.04447619134397954</v>
+        <v>4.0583119020438943E-2</v>
       </c>
       <c r="C12">
-        <v>0.1700666437450546</v>
+        <v>0.16030513228721679</v>
       </c>
       <c r="D12">
-        <v>0.2066130032248926</v>
+        <v>0.21276109103877419</v>
       </c>
       <c r="E12">
-        <v>0.4160587768563995</v>
+        <v>0.40872819541111632</v>
       </c>
       <c r="F12">
-        <v>0.3663780309195006</v>
+        <v>0.35305339603103442</v>
       </c>
       <c r="G12">
-        <v>0.4441601834519985</v>
+        <v>0.44177958508556298</v>
       </c>
       <c r="H12">
-        <v>0.3721502157690783</v>
+        <v>0.36133601804360638</v>
       </c>
       <c r="I12">
-        <v>0.3329580972267034</v>
+        <v>0.33566407686905719</v>
       </c>
       <c r="J12">
-        <v>0.3090886126920661</v>
+        <v>0.31425913090149521</v>
       </c>
       <c r="K12">
-        <v>0.3063301053317433</v>
+        <v>0.31519755550726009</v>
       </c>
       <c r="L12">
-        <v>0.317731822002623</v>
+        <v>0.33125719679070648</v>
       </c>
       <c r="M12">
-        <v>0.3338393672699039</v>
+        <v>0.34821036316023152</v>
       </c>
       <c r="N12">
-        <v>0.3741825266275234</v>
+        <v>0.39360423454022542</v>
       </c>
       <c r="O12">
-        <v>0.4089364514923133</v>
+        <v>0.43085850555921462</v>
       </c>
       <c r="P12">
-        <v>0.4703620992886055</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
-        </is>
+        <v>0.50438832269644429</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>27</v>
       </c>
       <c r="B13">
-        <v>0.06261050216397607</v>
+        <v>5.8215294348087747E-2</v>
       </c>
       <c r="C13">
-        <v>0.2975907519866995</v>
+        <v>0.29537534920858038</v>
       </c>
       <c r="D13">
-        <v>0.2877311587416514</v>
+        <v>0.29848599642016033</v>
       </c>
       <c r="E13">
-        <v>0.4421020998829692</v>
+        <v>0.45068269134521283</v>
       </c>
       <c r="F13">
-        <v>0.4807896205755514</v>
+        <v>0.4900011711353699</v>
       </c>
       <c r="G13">
-        <v>0.4587878746696634</v>
+        <v>0.46106158988518509</v>
       </c>
       <c r="H13">
-        <v>0.5453248621813725</v>
+        <v>0.54934017777774258</v>
       </c>
       <c r="I13">
-        <v>0.55166780250654</v>
+        <v>0.55600377201665718</v>
       </c>
       <c r="J13">
-        <v>0.5438808607845338</v>
+        <v>0.53670263269438101</v>
       </c>
       <c r="K13">
-        <v>0.5147783048545211</v>
+        <v>0.51111533912460549</v>
       </c>
       <c r="L13">
-        <v>0.5273766197162721</v>
+        <v>0.52094452811208658</v>
       </c>
       <c r="M13">
-        <v>0.5395243343657288</v>
+        <v>0.52226375068424924</v>
       </c>
       <c r="N13">
-        <v>0.5459551209787161</v>
+        <v>0.53415250740569842</v>
       </c>
       <c r="O13">
-        <v>0.549683357996831</v>
+        <v>0.5365289614528419</v>
       </c>
       <c r="P13">
-        <v>0.5744811910495108</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-        </is>
+        <v>0.56738728488672674</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>28</v>
       </c>
       <c r="B14">
-        <v>0.05027095809080803</v>
+        <v>5.0718071640209812E-2</v>
       </c>
       <c r="C14">
-        <v>0.07642322209012464</v>
+        <v>7.7389450019946682E-2</v>
       </c>
       <c r="D14">
-        <v>0.1555281913516284</v>
+        <v>0.15582012841936549</v>
       </c>
       <c r="E14">
-        <v>0.1887445013009748</v>
+        <v>0.18497952323531119</v>
       </c>
       <c r="F14">
-        <v>0.3069170741815324</v>
+        <v>0.299484129653034</v>
       </c>
       <c r="G14">
-        <v>0.3406115334704232</v>
+        <v>0.34360583350085472</v>
       </c>
       <c r="H14">
-        <v>0.3059682287476592</v>
+        <v>0.30163798571377942</v>
       </c>
       <c r="I14">
-        <v>0.2593974302832304</v>
+        <v>0.25223949596768569</v>
       </c>
       <c r="J14">
-        <v>0.3263866469108909</v>
+        <v>0.30720082552548011</v>
       </c>
       <c r="K14">
-        <v>0.3528932582879547</v>
+        <v>0.35272910167742022</v>
       </c>
       <c r="L14">
-        <v>0.3599363194579421</v>
+        <v>0.35505801841344542</v>
       </c>
       <c r="M14">
-        <v>0.348756503505362</v>
+        <v>0.34534664719516239</v>
       </c>
       <c r="N14">
-        <v>0.3337412098676963</v>
+        <v>0.32144518117458781</v>
       </c>
       <c r="O14">
-        <v>0.3396956056816117</v>
+        <v>0.32955057395397291</v>
       </c>
       <c r="P14">
-        <v>0.3361246407791394</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-        </is>
+        <v>0.33626705881915459</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>29</v>
       </c>
       <c r="B15">
-        <v>0.05392207774531405</v>
+        <v>5.2158215853461913E-2</v>
       </c>
       <c r="C15">
-        <v>0.08037960362776046</v>
+        <v>7.7335687775591064E-2</v>
       </c>
       <c r="D15">
-        <v>0.1584588310902402</v>
+        <v>0.15674430661808109</v>
       </c>
       <c r="E15">
-        <v>0.190038465642524</v>
+        <v>0.19078222364556019</v>
       </c>
       <c r="F15">
-        <v>0.3059757274329101</v>
+        <v>0.30405952496710548</v>
       </c>
       <c r="G15">
-        <v>0.3413622682736186</v>
+        <v>0.33399835828965568</v>
       </c>
       <c r="H15">
-        <v>0.2966005455390071</v>
+        <v>0.29528747820913998</v>
       </c>
       <c r="I15">
-        <v>0.2672207219621744</v>
+        <v>0.25151277523621968</v>
       </c>
       <c r="J15">
-        <v>0.3219843364678077</v>
+        <v>0.31169809813854021</v>
       </c>
       <c r="K15">
-        <v>0.3492516383106662</v>
+        <v>0.35139075503756911</v>
       </c>
       <c r="L15">
-        <v>0.3587061925465596</v>
+        <v>0.35826617410454797</v>
       </c>
       <c r="M15">
-        <v>0.3548177736867298</v>
+        <v>0.36088596132255701</v>
       </c>
       <c r="N15">
-        <v>0.3311109667694372</v>
+        <v>0.33595271273526361</v>
       </c>
       <c r="O15">
-        <v>0.339611065648223</v>
+        <v>0.3405732552659857</v>
       </c>
       <c r="P15">
-        <v>0.3385779703350835</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
-        </is>
+        <v>0.34532946633856593</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>30</v>
       </c>
       <c r="B16">
-        <v>0.04664888461001213</v>
+        <v>4.5605043720765591E-2</v>
       </c>
       <c r="C16">
-        <v>0.07326891504712127</v>
+        <v>7.2702695997147002E-2</v>
       </c>
       <c r="D16">
-        <v>0.1521185827590552</v>
+        <v>0.15577410426201499</v>
       </c>
       <c r="E16">
-        <v>0.182514240441684</v>
+        <v>0.1914322814335537</v>
       </c>
       <c r="F16">
-        <v>0.290020099723902</v>
+        <v>0.3014987418747509</v>
       </c>
       <c r="G16">
-        <v>0.3365131760799979</v>
+        <v>0.34412275567039641</v>
       </c>
       <c r="H16">
-        <v>0.3047279497202995</v>
+        <v>0.30310616349256608</v>
       </c>
       <c r="I16">
-        <v>0.257137786272208</v>
+        <v>0.26114890409545938</v>
       </c>
       <c r="J16">
-        <v>0.3051574331953153</v>
+        <v>0.3127815865194587</v>
       </c>
       <c r="K16">
-        <v>0.3417476173633757</v>
+        <v>0.3566276731356518</v>
       </c>
       <c r="L16">
-        <v>0.3595511662701086</v>
+        <v>0.36852338206801288</v>
       </c>
       <c r="M16">
-        <v>0.3522203621096304</v>
+        <v>0.3509501964549519</v>
       </c>
       <c r="N16">
-        <v>0.3240611020332532</v>
+        <v>0.33352753068754909</v>
       </c>
       <c r="O16">
-        <v>0.3249415704943849</v>
+        <v>0.33819281794173051</v>
       </c>
       <c r="P16">
-        <v>0.329710347113119</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-        </is>
+        <v>0.33515561541846511</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>31</v>
       </c>
       <c r="B17">
-        <v>0.04790643100872283</v>
+        <v>4.9663778034089057E-2</v>
       </c>
       <c r="C17">
-        <v>0.07686522950475097</v>
+        <v>7.801966949097365E-2</v>
       </c>
       <c r="D17">
-        <v>0.1576864453582564</v>
+        <v>0.15647445845928509</v>
       </c>
       <c r="E17">
-        <v>0.191013894355692</v>
+        <v>0.18846523882794819</v>
       </c>
       <c r="F17">
-        <v>0.289548863418194</v>
+        <v>0.29931357213401821</v>
       </c>
       <c r="G17">
-        <v>0.3366530547772572</v>
+        <v>0.33542811679653622</v>
       </c>
       <c r="H17">
-        <v>0.297143744278497</v>
+        <v>0.29723283204424139</v>
       </c>
       <c r="I17">
-        <v>0.245833709477977</v>
+        <v>0.25525349335757658</v>
       </c>
       <c r="J17">
-        <v>0.3042249333866919</v>
+        <v>0.30839443412308809</v>
       </c>
       <c r="K17">
-        <v>0.3464284633457706</v>
+        <v>0.35098105766406729</v>
       </c>
       <c r="L17">
-        <v>0.3671391756407926</v>
+        <v>0.35788308261211388</v>
       </c>
       <c r="M17">
-        <v>0.3521233180816149</v>
+        <v>0.34863020266186961</v>
       </c>
       <c r="N17">
-        <v>0.3436127231159527</v>
+        <v>0.33958550022867412</v>
       </c>
       <c r="O17">
-        <v>0.3500620387040658</v>
+        <v>0.34988771183134543</v>
       </c>
       <c r="P17">
-        <v>0.3533993865842961</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-        </is>
+        <v>0.34639234779240508</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>32</v>
       </c>
       <c r="B18">
-        <v>0.04304763026957647</v>
+        <v>4.5693139847216541E-2</v>
       </c>
       <c r="C18">
-        <v>0.1735714312457759</v>
+        <v>0.16969609042046899</v>
       </c>
       <c r="D18">
-        <v>0.2151166860059256</v>
+        <v>0.22873487522078689</v>
       </c>
       <c r="E18">
-        <v>0.4334453091851413</v>
+        <v>0.43294644583507341</v>
       </c>
       <c r="F18">
-        <v>0.3318260239118915</v>
+        <v>0.34203294318949501</v>
       </c>
       <c r="G18">
-        <v>0.3939112472911001</v>
+        <v>0.40259015022091083</v>
       </c>
       <c r="H18">
-        <v>0.4380192541253982</v>
+        <v>0.45168258228285402</v>
       </c>
       <c r="I18">
-        <v>0.3757840428054824</v>
+        <v>0.38597025157837428</v>
       </c>
       <c r="J18">
-        <v>0.327251317269264</v>
+        <v>0.32942267377365442</v>
       </c>
       <c r="K18">
-        <v>0.3181851484333762</v>
+        <v>0.32280465626898452</v>
       </c>
       <c r="L18">
-        <v>0.3409100480689309</v>
+        <v>0.34305811740688569</v>
       </c>
       <c r="M18">
-        <v>0.3532559724747234</v>
+        <v>0.36347698324841982</v>
       </c>
       <c r="N18">
-        <v>0.4072002027541485</v>
+        <v>0.41136865841956272</v>
       </c>
       <c r="O18">
-        <v>0.4520461519661561</v>
+        <v>0.46202027019036862</v>
       </c>
       <c r="P18">
-        <v>0.4940222878048772</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
-        </is>
+        <v>0.49956667239011171</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>33</v>
       </c>
       <c r="B19">
-        <v>0.04417430208801208</v>
+        <v>4.6848510711796569E-2</v>
       </c>
       <c r="C19">
-        <v>0.1958710567660968</v>
+        <v>0.18859505981466751</v>
       </c>
       <c r="D19">
-        <v>0.2109897303077429</v>
+        <v>0.19142360242155379</v>
       </c>
       <c r="E19">
-        <v>0.4617027682871864</v>
+        <v>0.44482875769646613</v>
       </c>
       <c r="F19">
-        <v>0.3020456258756548</v>
+        <v>0.28261555751694828</v>
       </c>
       <c r="G19">
-        <v>0.3174250610331316</v>
+        <v>0.31947607667850669</v>
       </c>
       <c r="H19">
-        <v>0.2820043288851228</v>
+        <v>0.28949445528580747</v>
       </c>
       <c r="I19">
-        <v>0.268434856376719</v>
+        <v>0.27415055333305632</v>
       </c>
       <c r="J19">
-        <v>0.2655374724131535</v>
+        <v>0.26452995016099812</v>
       </c>
       <c r="K19">
-        <v>0.2844623695912794</v>
+        <v>0.2791895547833641</v>
       </c>
       <c r="L19">
-        <v>0.308796876942658</v>
+        <v>0.30254467290520748</v>
       </c>
       <c r="M19">
-        <v>0.3327964419287646</v>
+        <v>0.32875850920809419</v>
       </c>
       <c r="N19">
-        <v>0.3705356140094983</v>
+        <v>0.37058720628247038</v>
       </c>
       <c r="O19">
-        <v>0.3819874769173189</v>
+        <v>0.38061838731672409</v>
       </c>
       <c r="P19">
-        <v>0.4193121638008007</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-        </is>
+        <v>0.41723026237465111</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>34</v>
       </c>
       <c r="B20">
-        <v>0.04284921055280411</v>
+        <v>4.1132109440790127E-2</v>
       </c>
       <c r="C20">
-        <v>0.2339946617047228</v>
+        <v>0.2265634533829182</v>
       </c>
       <c r="D20">
-        <v>0.2269782832932368</v>
+        <v>0.22131563879171179</v>
       </c>
       <c r="E20">
-        <v>0.258466559153569</v>
+        <v>0.25200551840374741</v>
       </c>
       <c r="F20">
-        <v>0.2541150575331637</v>
+        <v>0.24535401394621001</v>
       </c>
       <c r="G20">
-        <v>0.3376126165980767</v>
+        <v>0.31443776725889322</v>
       </c>
       <c r="H20">
-        <v>0.2911449608697473</v>
+        <v>0.27440248975138742</v>
       </c>
       <c r="I20">
-        <v>0.2821159710633155</v>
+        <v>0.26769446761477778</v>
       </c>
       <c r="J20">
-        <v>0.2662891773550177</v>
+        <v>0.25605946507929939</v>
       </c>
       <c r="K20">
-        <v>0.2895538165060701</v>
+        <v>0.27928814044107542</v>
       </c>
       <c r="L20">
-        <v>0.3160419586963635</v>
+        <v>0.31277504651515209</v>
       </c>
       <c r="M20">
-        <v>0.3502621071878613</v>
+        <v>0.34979366998400552</v>
       </c>
       <c r="N20">
-        <v>0.3307697432820604</v>
+        <v>0.32698922381726347</v>
       </c>
       <c r="O20">
-        <v>0.3531120088106149</v>
+        <v>0.35524310443471341</v>
       </c>
       <c r="P20">
-        <v>0.3743896187317929</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>0.37579171513727078</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>35</v>
       </c>
       <c r="B21">
-        <v>0.05653671480929614</v>
+        <v>5.7979858445694289E-2</v>
       </c>
       <c r="C21">
-        <v>0.338060457377255</v>
+        <v>0.34226982600440992</v>
       </c>
       <c r="D21">
-        <v>0.4042615311971539</v>
+        <v>0.41111742683491831</v>
       </c>
       <c r="E21">
-        <v>0.3335062605363158</v>
+        <v>0.32458608995284988</v>
       </c>
       <c r="F21">
-        <v>0.3326134881511971</v>
+        <v>0.32310931375238627</v>
       </c>
       <c r="G21">
-        <v>0.3752173042017648</v>
+        <v>0.36604844425309851</v>
       </c>
       <c r="H21">
-        <v>0.429243526268769</v>
+        <v>0.41822728446076612</v>
       </c>
       <c r="I21">
-        <v>0.4609472623731067</v>
+        <v>0.44819707510404277</v>
       </c>
       <c r="J21">
-        <v>0.4328565958281415</v>
+        <v>0.4244643423076217</v>
       </c>
       <c r="K21">
-        <v>0.4434765708249782</v>
+        <v>0.43544428508545457</v>
       </c>
       <c r="L21">
-        <v>0.4595674181720638</v>
+        <v>0.45251553751583812</v>
       </c>
       <c r="M21">
-        <v>0.5028969284896093</v>
+        <v>0.49831161000244228</v>
       </c>
       <c r="N21">
-        <v>0.5656593334519245</v>
+        <v>0.57270931713099327</v>
       </c>
       <c r="O21">
-        <v>0.626010475226663</v>
+        <v>0.63212362556364277</v>
       </c>
       <c r="P21">
-        <v>0.6355569504279895</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>0.63632197089479081</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>36</v>
       </c>
       <c r="B22">
-        <v>0.05644391737128929</v>
+        <v>5.339154393974746E-2</v>
       </c>
       <c r="C22">
-        <v>0.3365538355449278</v>
+        <v>0.32985551095834742</v>
       </c>
       <c r="D22">
-        <v>0.394856356624914</v>
+        <v>0.39751800711880231</v>
       </c>
       <c r="E22">
-        <v>0.3088040259873936</v>
+        <v>0.31118910415516088</v>
       </c>
       <c r="F22">
-        <v>0.3147724370078919</v>
+        <v>0.31817814917215759</v>
       </c>
       <c r="G22">
-        <v>0.3594051589939151</v>
+        <v>0.35865454525138418</v>
       </c>
       <c r="H22">
-        <v>0.4359646447975319</v>
+        <v>0.43522851483757291</v>
       </c>
       <c r="I22">
-        <v>0.4849489258923366</v>
+        <v>0.48588104011829042</v>
       </c>
       <c r="J22">
-        <v>0.4744710263679416</v>
+        <v>0.46698672111986461</v>
       </c>
       <c r="K22">
-        <v>0.4827262931210594</v>
+        <v>0.47845466467135039</v>
       </c>
       <c r="L22">
-        <v>0.5206850334384707</v>
+        <v>0.50956741701406982</v>
       </c>
       <c r="M22">
-        <v>0.5484138366106824</v>
+        <v>0.5340444720108144</v>
       </c>
       <c r="N22">
-        <v>0.6012456621385573</v>
+        <v>0.58533147818327658</v>
       </c>
       <c r="O22">
-        <v>0.6271378139626057</v>
+        <v>0.60704062624832855</v>
       </c>
       <c r="P22">
-        <v>0.6461711709746838</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>0.62454864506259522</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>37</v>
       </c>
       <c r="B23">
-        <v>0.04486747003956511</v>
+        <v>5.2725282777001697E-2</v>
       </c>
       <c r="C23">
-        <v>0.2622818540564522</v>
+        <v>0.268441555111601</v>
       </c>
       <c r="D23">
-        <v>0.2650069795290623</v>
+        <v>0.29271543226173602</v>
       </c>
       <c r="E23">
-        <v>0.2181585693451353</v>
+        <v>0.22225684153764891</v>
       </c>
       <c r="F23">
-        <v>0.2884794746959213</v>
+        <v>0.29859952246631682</v>
       </c>
       <c r="G23">
-        <v>0.2833511991024185</v>
+        <v>0.28832693353851208</v>
       </c>
       <c r="H23">
-        <v>0.301482298919881</v>
+        <v>0.30487241515173669</v>
       </c>
       <c r="I23">
-        <v>0.3450827149249729</v>
+        <v>0.35298761619129537</v>
       </c>
       <c r="J23">
-        <v>0.3662614776156694</v>
+        <v>0.3697440882790789</v>
       </c>
       <c r="K23">
-        <v>0.4315413717226039</v>
+        <v>0.43136344495665718</v>
       </c>
       <c r="L23">
-        <v>0.467731718005481</v>
+        <v>0.46980829562441762</v>
       </c>
       <c r="M23">
-        <v>0.5297507855581582</v>
+        <v>0.52998781761621494</v>
       </c>
       <c r="N23">
-        <v>0.5515475809591412</v>
+        <v>0.55065009797035913</v>
       </c>
       <c r="O23">
-        <v>0.5687978068628966</v>
+        <v>0.56746172128814054</v>
       </c>
       <c r="P23">
-        <v>0.6024408876620548</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>adj_red_c(950,20,1)_snv_sder_c(1,3,15)_</t>
-        </is>
+        <v>0.60564281871260839</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>38</v>
       </c>
       <c r="B24">
-        <v>0.1034109198290691</v>
+        <v>6.9446347666903455E-2</v>
       </c>
       <c r="C24">
-        <v>0.1469524185218946</v>
+        <v>0.12988701412066381</v>
       </c>
       <c r="D24">
-        <v>0.1977443190989291</v>
+        <v>0.2194777511801112</v>
       </c>
       <c r="E24">
-        <v>0.2964798032407699</v>
+        <v>0.2161036868243453</v>
       </c>
       <c r="F24">
-        <v>0.3894485419447792</v>
+        <v>0.2297761329879916</v>
       </c>
       <c r="G24">
-        <v>0.5807821546342697</v>
+        <v>0.21941810079128579</v>
       </c>
       <c r="H24">
-        <v>0.6054864430544089</v>
+        <v>0.30786748750374038</v>
       </c>
       <c r="I24">
-        <v>0.6949531437266794</v>
+        <v>0.44724604380842259</v>
       </c>
       <c r="J24">
-        <v>0.8073963829184222</v>
+        <v>0.47072435083998337</v>
       </c>
       <c r="K24">
-        <v>1.008876905866965</v>
+        <v>0.46360169212938129</v>
       </c>
       <c r="L24">
-        <v>1.023589330527838</v>
+        <v>0.47849326721974589</v>
       </c>
       <c r="M24">
-        <v>1.099647301209441</v>
+        <v>0.57434865161094184</v>
       </c>
       <c r="N24">
-        <v>1.228509155281901</v>
+        <v>0.68587994527939655</v>
       </c>
       <c r="O24">
-        <v>1.33114613992754</v>
+        <v>0.76917506538698044</v>
       </c>
       <c r="P24">
-        <v>1.471373251064128</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>adj_red_c(950,20,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>0.87748519014092496</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>39</v>
       </c>
       <c r="B25">
-        <v>0.2382746641053781</v>
+        <v>7.1882715704221375E-2</v>
       </c>
       <c r="C25">
-        <v>0.3444317422076331</v>
+        <v>0.13800514035031741</v>
       </c>
       <c r="D25">
-        <v>0.3954122272763885</v>
+        <v>0.24332826032536181</v>
       </c>
       <c r="E25">
-        <v>0.4093038213081667</v>
+        <v>0.23458663059346591</v>
       </c>
       <c r="F25">
-        <v>0.6148450878934525</v>
+        <v>0.2165112935498032</v>
       </c>
       <c r="G25">
-        <v>0.736706603103042</v>
+        <v>0.2564458312591737</v>
       </c>
       <c r="H25">
-        <v>0.7900602188212057</v>
+        <v>0.5480425440695913</v>
       </c>
       <c r="I25">
-        <v>0.8153819312873283</v>
+        <v>0.52512516209659288</v>
       </c>
       <c r="J25">
-        <v>0.8842218272049924</v>
+        <v>0.51501797131892257</v>
       </c>
       <c r="K25">
-        <v>1.027560154489822</v>
+        <v>0.49549068479470609</v>
       </c>
       <c r="L25">
-        <v>1.114209500206629</v>
+        <v>0.49950223655067222</v>
       </c>
       <c r="M25">
-        <v>1.25034107070512</v>
+        <v>0.53714170089840252</v>
       </c>
       <c r="N25">
-        <v>1.39136208683369</v>
+        <v>0.62019920742997847</v>
       </c>
       <c r="O25">
-        <v>1.473406456493909</v>
+        <v>0.71330707705353424</v>
       </c>
       <c r="P25">
-        <v>1.530448475729935</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>adj_red_c(950,750,1)_snv_sder_c(1,3,15)_</t>
-        </is>
+        <v>0.80655042011626887</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>40</v>
       </c>
       <c r="B26">
-        <v>0.09908485819786719</v>
+        <v>7.9347360529910552E-2</v>
       </c>
       <c r="C26">
-        <v>0.1550102912703344</v>
+        <v>0.1580148201164793</v>
       </c>
       <c r="D26">
-        <v>0.1305086878043848</v>
+        <v>0.20329686232075769</v>
       </c>
       <c r="E26">
-        <v>0.1436021321381574</v>
+        <v>0.19821039854216019</v>
       </c>
       <c r="F26">
-        <v>0.2495483526458516</v>
+        <v>0.26417975481023842</v>
       </c>
       <c r="G26">
-        <v>0.2568331439127735</v>
+        <v>0.26291079998942402</v>
       </c>
       <c r="H26">
-        <v>0.2823304008278617</v>
+        <v>0.37344082469500012</v>
       </c>
       <c r="I26">
-        <v>0.3427872652500851</v>
+        <v>0.60785735223695181</v>
       </c>
       <c r="J26">
-        <v>0.3576756294268326</v>
+        <v>0.50583840133820857</v>
       </c>
       <c r="K26">
-        <v>0.4051328874395745</v>
+        <v>0.51124314930185899</v>
       </c>
       <c r="L26">
-        <v>0.457831044764084</v>
+        <v>0.55070167358944899</v>
       </c>
       <c r="M26">
-        <v>0.4727284300345447</v>
+        <v>0.64101573112372801</v>
       </c>
       <c r="N26">
-        <v>0.5318862209634109</v>
+        <v>0.70760756237618738</v>
       </c>
       <c r="O26">
-        <v>0.6094031571596334</v>
+        <v>0.78929521505099276</v>
       </c>
       <c r="P26">
-        <v>0.6407557102476871</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>adj_red_c(950,750,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>0.90253027547812492</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>41</v>
       </c>
       <c r="B27">
-        <v>0.1620646903971714</v>
+        <v>7.7020972979223293E-2</v>
       </c>
       <c r="C27">
-        <v>0.3173437248974592</v>
+        <v>0.13971193158635939</v>
       </c>
       <c r="D27">
-        <v>0.1505623269748935</v>
+        <v>0.18172741459534569</v>
       </c>
       <c r="E27">
-        <v>0.1739876293255878</v>
+        <v>0.1643012974579238</v>
       </c>
       <c r="F27">
-        <v>0.2662164903437321</v>
+        <v>0.21738782225893599</v>
       </c>
       <c r="G27">
-        <v>0.3318972199762984</v>
+        <v>0.2090293824360267</v>
       </c>
       <c r="H27">
-        <v>0.4032100648351131</v>
+        <v>0.2451302659389081</v>
       </c>
       <c r="I27">
-        <v>0.5372374205235192</v>
+        <v>0.42478475838944779</v>
       </c>
       <c r="J27">
-        <v>0.5698576597860578</v>
+        <v>0.35871576864014543</v>
       </c>
       <c r="K27">
-        <v>0.5959062082355955</v>
+        <v>0.34494447222475921</v>
       </c>
       <c r="L27">
-        <v>0.5800082036153487</v>
+        <v>0.3233185641548374</v>
       </c>
       <c r="M27">
-        <v>0.5778430484343949</v>
+        <v>0.38600450692706939</v>
       </c>
       <c r="N27">
-        <v>0.6028297601976966</v>
+        <v>0.38356062497861237</v>
       </c>
       <c r="O27">
-        <v>0.6556481304555367</v>
+        <v>0.42615153957926538</v>
       </c>
       <c r="P27">
-        <v>0.6864757634299277</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
-        </is>
+        <v>0.45416522356453559</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>42</v>
       </c>
       <c r="B28">
-        <v>0.06570764315186074</v>
+        <v>7.033232437325769E-2</v>
       </c>
       <c r="C28">
-        <v>0.1260303665767638</v>
+        <v>0.13031635139518519</v>
       </c>
       <c r="D28">
-        <v>0.217380376890624</v>
+        <v>0.22709331144026851</v>
       </c>
       <c r="E28">
-        <v>0.2095863268687897</v>
+        <v>0.21242283323030331</v>
       </c>
       <c r="F28">
-        <v>0.2254285865864742</v>
+        <v>0.19835489902293191</v>
       </c>
       <c r="G28">
-        <v>0.2137667510850345</v>
+        <v>0.21490470575489229</v>
       </c>
       <c r="H28">
-        <v>0.3045445112060176</v>
+        <v>0.39318807337893258</v>
       </c>
       <c r="I28">
-        <v>0.4374643034388481</v>
+        <v>0.40650746117125158</v>
       </c>
       <c r="J28">
-        <v>0.4846305620308974</v>
+        <v>0.38950915037549388</v>
       </c>
       <c r="K28">
-        <v>0.4613885173323259</v>
+        <v>0.3423881567779814</v>
       </c>
       <c r="L28">
-        <v>0.4767105780082181</v>
+        <v>0.34143664879439428</v>
       </c>
       <c r="M28">
-        <v>0.57354379191869</v>
+        <v>0.33378682830635159</v>
       </c>
       <c r="N28">
-        <v>0.6798900461119397</v>
+        <v>0.37532615922879192</v>
       </c>
       <c r="O28">
-        <v>0.7591500910769092</v>
+        <v>0.4107321841234659</v>
       </c>
       <c r="P28">
-        <v>0.86865358308392</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
-        </is>
+        <v>0.4422320511243103</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>43</v>
       </c>
       <c r="B29">
-        <v>0.07468248532633814</v>
+        <v>7.1797607124829396E-2</v>
       </c>
       <c r="C29">
-        <v>0.1371200004455143</v>
+        <v>0.1380104689255936</v>
       </c>
       <c r="D29">
-        <v>0.2419853731229922</v>
+        <v>0.23439053507208191</v>
       </c>
       <c r="E29">
-        <v>0.2322481430235171</v>
+        <v>0.21711859018919191</v>
       </c>
       <c r="F29">
-        <v>0.2193739351826484</v>
+        <v>0.19911617700981529</v>
       </c>
       <c r="G29">
-        <v>0.2470775924296489</v>
+        <v>0.2092468717423312</v>
       </c>
       <c r="H29">
-        <v>0.5331670501908701</v>
+        <v>0.37838249780950761</v>
       </c>
       <c r="I29">
-        <v>0.5106857265402862</v>
+        <v>0.37990235219684498</v>
       </c>
       <c r="J29">
-        <v>0.5036161824609836</v>
+        <v>0.37666304709716458</v>
       </c>
       <c r="K29">
-        <v>0.4850284201896578</v>
+        <v>0.32635755765560698</v>
       </c>
       <c r="L29">
-        <v>0.4860207788085383</v>
+        <v>0.32934781124847973</v>
       </c>
       <c r="M29">
-        <v>0.5190219676826066</v>
+        <v>0.31920747474341937</v>
       </c>
       <c r="N29">
-        <v>0.5983961790846576</v>
+        <v>0.36049740558159371</v>
       </c>
       <c r="O29">
-        <v>0.6919327640742713</v>
+        <v>0.38865014353513239</v>
       </c>
       <c r="P29">
-        <v>0.7774953912884077</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
-        </is>
+        <v>0.41892612180061339</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>44</v>
       </c>
       <c r="B30">
-        <v>0.07758479740413186</v>
+        <v>7.2380327998954011E-2</v>
       </c>
       <c r="C30">
-        <v>0.147778389480469</v>
+        <v>0.1357497423513036</v>
       </c>
       <c r="D30">
-        <v>0.195417999667521</v>
+        <v>0.2296946078859842</v>
       </c>
       <c r="E30">
-        <v>0.1865370027127148</v>
+        <v>0.21461866331066129</v>
       </c>
       <c r="F30">
-        <v>0.2578919042542825</v>
+        <v>0.20466254056204081</v>
       </c>
       <c r="G30">
-        <v>0.2590709905417387</v>
+        <v>0.2170835832937128</v>
       </c>
       <c r="H30">
-        <v>0.3802942786134272</v>
+        <v>0.37749969081124918</v>
       </c>
       <c r="I30">
-        <v>0.6124978789854471</v>
+        <v>0.38731478846296991</v>
       </c>
       <c r="J30">
-        <v>0.5100035050664894</v>
+        <v>0.38524086177024208</v>
       </c>
       <c r="K30">
-        <v>0.5096379848084002</v>
+        <v>0.33500748131103741</v>
       </c>
       <c r="L30">
-        <v>0.5436397633094953</v>
+        <v>0.33685827208680807</v>
       </c>
       <c r="M30">
-        <v>0.6316518676120157</v>
+        <v>0.331023652137032</v>
       </c>
       <c r="N30">
-        <v>0.6999205964422911</v>
+        <v>0.36088262117421632</v>
       </c>
       <c r="O30">
-        <v>0.7830821826943373</v>
+        <v>0.38852897526944918</v>
       </c>
       <c r="P30">
-        <v>0.894906658432096</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-        </is>
+        <v>0.40873248744891111</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>45</v>
       </c>
       <c r="B31">
-        <v>0.07737038176184441</v>
+        <v>7.1669004092782498E-2</v>
       </c>
       <c r="C31">
-        <v>0.1536156929089882</v>
+        <v>0.12993085346946151</v>
       </c>
       <c r="D31">
-        <v>0.1993376768644302</v>
+        <v>0.22509123747601839</v>
       </c>
       <c r="E31">
-        <v>0.1817555574917581</v>
+        <v>0.20763816738525151</v>
       </c>
       <c r="F31">
-        <v>0.2348279213259654</v>
+        <v>0.19592352470001831</v>
       </c>
       <c r="G31">
-        <v>0.2317595111294339</v>
+        <v>0.20634234040097099</v>
       </c>
       <c r="H31">
-        <v>0.2593564178992169</v>
+        <v>0.36030682979941547</v>
       </c>
       <c r="I31">
-        <v>0.459875195839906</v>
+        <v>0.36886355368831819</v>
       </c>
       <c r="J31">
-        <v>0.3754785819258644</v>
+        <v>0.3759897738284933</v>
       </c>
       <c r="K31">
-        <v>0.3517958060790221</v>
+        <v>0.33126021104118092</v>
       </c>
       <c r="L31">
-        <v>0.3323929231091362</v>
+        <v>0.33539349925446338</v>
       </c>
       <c r="M31">
-        <v>0.3783759343244373</v>
+        <v>0.32373569913025457</v>
       </c>
       <c r="N31">
-        <v>0.3831709942382087</v>
+        <v>0.35824051864360801</v>
       </c>
       <c r="O31">
-        <v>0.4292543326040635</v>
+        <v>0.38654923877356612</v>
       </c>
       <c r="P31">
-        <v>0.4523595033560238</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
-        </is>
+        <v>0.39436345388370991</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>46</v>
       </c>
       <c r="B32">
-        <v>0.07113976980825902</v>
+        <v>6.9592287227978541E-2</v>
       </c>
       <c r="C32">
-        <v>0.1313181084993424</v>
+        <v>0.1359948597968211</v>
       </c>
       <c r="D32">
-        <v>0.2284926266424842</v>
+        <v>0.234096202147451</v>
       </c>
       <c r="E32">
-        <v>0.2125582493868606</v>
+        <v>0.22410110196885449</v>
       </c>
       <c r="F32">
-        <v>0.2008162056782984</v>
+        <v>0.20485296638564329</v>
       </c>
       <c r="G32">
-        <v>0.2179788691036534</v>
+        <v>0.22145278970289989</v>
       </c>
       <c r="H32">
-        <v>0.3984366198419584</v>
+        <v>0.42059361979999982</v>
       </c>
       <c r="I32">
-        <v>0.397699746954655</v>
+        <v>0.41165010380243461</v>
       </c>
       <c r="J32">
-        <v>0.3857470137800006</v>
+        <v>0.404621553562381</v>
       </c>
       <c r="K32">
-        <v>0.3612108294753095</v>
+        <v>0.37224462982160178</v>
       </c>
       <c r="L32">
-        <v>0.3465237848538946</v>
+        <v>0.36397707570719301</v>
       </c>
       <c r="M32">
-        <v>0.3435030300022971</v>
+        <v>0.36799779825861018</v>
       </c>
       <c r="N32">
-        <v>0.3746004528909048</v>
+        <v>0.41905717946323912</v>
       </c>
       <c r="O32">
-        <v>0.4168563035671892</v>
+        <v>0.47778378223119911</v>
       </c>
       <c r="P32">
-        <v>0.4454472926607689</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
-        </is>
+        <v>0.53841167462800466</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>47</v>
       </c>
       <c r="B33">
-        <v>0.07291164992198115</v>
+        <v>6.892750345540942E-2</v>
       </c>
       <c r="C33">
-        <v>0.1363594970330547</v>
+        <v>0.13073583441010239</v>
       </c>
       <c r="D33">
-        <v>0.2318248385578143</v>
+        <v>0.22743337470343539</v>
       </c>
       <c r="E33">
-        <v>0.2164387876714761</v>
+        <v>0.21129873992337311</v>
       </c>
       <c r="F33">
-        <v>0.202638075771617</v>
+        <v>0.19638080852621109</v>
       </c>
       <c r="G33">
-        <v>0.2094453963340044</v>
+        <v>0.2118215306009055</v>
       </c>
       <c r="H33">
-        <v>0.380026628230978</v>
+        <v>0.40782081764493378</v>
       </c>
       <c r="I33">
-        <v>0.3778754685460084</v>
+        <v>0.39680275506378582</v>
       </c>
       <c r="J33">
-        <v>0.3700411346476431</v>
+        <v>0.38543495939471362</v>
       </c>
       <c r="K33">
-        <v>0.323270350218912</v>
+        <v>0.35618517666836852</v>
       </c>
       <c r="L33">
-        <v>0.3247536766155174</v>
+        <v>0.35891555410673381</v>
       </c>
       <c r="M33">
-        <v>0.3202848228116953</v>
+        <v>0.35594449778830223</v>
       </c>
       <c r="N33">
-        <v>0.3531826004839733</v>
+        <v>0.39965661479020059</v>
       </c>
       <c r="O33">
-        <v>0.3826042064094257</v>
+        <v>0.44609589273621469</v>
       </c>
       <c r="P33">
-        <v>0.4069067440229491</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
-        </is>
+        <v>0.49948336726140508</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>48</v>
       </c>
       <c r="B34">
-        <v>0.06729292389907943</v>
+        <v>6.8050493819678454E-2</v>
       </c>
       <c r="C34">
-        <v>0.130144977018025</v>
+        <v>0.13392518109946719</v>
       </c>
       <c r="D34">
-        <v>0.2286429120521199</v>
+        <v>0.23113633884070869</v>
       </c>
       <c r="E34">
-        <v>0.2152697402200887</v>
+        <v>0.22166198745419199</v>
       </c>
       <c r="F34">
-        <v>0.1958206735774037</v>
+        <v>0.2042490869382669</v>
       </c>
       <c r="G34">
-        <v>0.2054304411093179</v>
+        <v>0.21873593215916889</v>
       </c>
       <c r="H34">
-        <v>0.3731379758075802</v>
+        <v>0.39693227416610172</v>
       </c>
       <c r="I34">
-        <v>0.3826212451777345</v>
+        <v>0.40531035612580979</v>
       </c>
       <c r="J34">
-        <v>0.3799216517510868</v>
+        <v>0.39271779473659812</v>
       </c>
       <c r="K34">
-        <v>0.3363375890838749</v>
+        <v>0.36570205585041288</v>
       </c>
       <c r="L34">
-        <v>0.3334113508925768</v>
+        <v>0.35762055110958002</v>
       </c>
       <c r="M34">
-        <v>0.3230785178087606</v>
+        <v>0.35622518440039658</v>
       </c>
       <c r="N34">
-        <v>0.3639164966006936</v>
+        <v>0.39310103841697158</v>
       </c>
       <c r="O34">
-        <v>0.3906883148304183</v>
+        <v>0.43714002915102868</v>
       </c>
       <c r="P34">
-        <v>0.4145929276672172</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
-        </is>
+        <v>0.48397531838110808</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>49</v>
       </c>
       <c r="B35">
-        <v>0.07036447400021914</v>
+        <v>7.3909585976651856E-2</v>
       </c>
       <c r="C35">
-        <v>0.1370193552139107</v>
+        <v>0.14420920715682631</v>
       </c>
       <c r="D35">
-        <v>0.2329697309418057</v>
+        <v>0.23815787371139399</v>
       </c>
       <c r="E35">
-        <v>0.2173407358820299</v>
+        <v>0.22431510166363411</v>
       </c>
       <c r="F35">
-        <v>0.2053752854557724</v>
+        <v>0.21026381638982289</v>
       </c>
       <c r="G35">
-        <v>0.2162902393863993</v>
+        <v>0.22702093900152609</v>
       </c>
       <c r="H35">
-        <v>0.3708744471870626</v>
+        <v>0.40404650892937671</v>
       </c>
       <c r="I35">
-        <v>0.390640623115628</v>
+        <v>0.40581316901291248</v>
       </c>
       <c r="J35">
-        <v>0.3961199267927491</v>
+        <v>0.39353032955703321</v>
       </c>
       <c r="K35">
-        <v>0.3470206908936629</v>
+        <v>0.36479577878372299</v>
       </c>
       <c r="L35">
-        <v>0.3471870712000744</v>
+        <v>0.36953368588604302</v>
       </c>
       <c r="M35">
-        <v>0.3333134366057893</v>
+        <v>0.35825846282516161</v>
       </c>
       <c r="N35">
-        <v>0.3618442912181873</v>
+        <v>0.38729765832366719</v>
       </c>
       <c r="O35">
-        <v>0.394430368079889</v>
+        <v>0.42593425945790953</v>
       </c>
       <c r="P35">
-        <v>0.4021954498267158</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-        </is>
+        <v>0.46083810665293862</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>50</v>
       </c>
       <c r="B36">
-        <v>0.07473056995451285</v>
+        <v>6.8461718169891675E-2</v>
       </c>
       <c r="C36">
-        <v>0.1453555661660082</v>
+        <v>0.13580317594275501</v>
       </c>
       <c r="D36">
-        <v>0.2389773942009832</v>
+        <v>0.22925581298229131</v>
       </c>
       <c r="E36">
-        <v>0.2219962896753369</v>
+        <v>0.208797231582007</v>
       </c>
       <c r="F36">
-        <v>0.2132423582402115</v>
+        <v>0.19734356135418801</v>
       </c>
       <c r="G36">
-        <v>0.229941011046015</v>
+        <v>0.21024453811745089</v>
       </c>
       <c r="H36">
-        <v>0.4357483394134003</v>
+        <v>0.34166372034355069</v>
       </c>
       <c r="I36">
-        <v>0.4169324684827601</v>
+        <v>0.35891410005160951</v>
       </c>
       <c r="J36">
-        <v>0.4044252323491563</v>
+        <v>0.35800116867047421</v>
       </c>
       <c r="K36">
-        <v>0.3678641912861077</v>
+        <v>0.3293115121510316</v>
       </c>
       <c r="L36">
-        <v>0.3636656687322286</v>
+        <v>0.3309908040046432</v>
       </c>
       <c r="M36">
-        <v>0.3549039319481156</v>
+        <v>0.32516086531930261</v>
       </c>
       <c r="N36">
-        <v>0.3994495361098796</v>
+        <v>0.35014238392506358</v>
       </c>
       <c r="O36">
-        <v>0.4515160552941564</v>
+        <v>0.3898122213154499</v>
       </c>
       <c r="P36">
-        <v>0.5089224217314906</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
-        </is>
+        <v>0.40188123165053319</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>51</v>
       </c>
       <c r="B37">
-        <v>0.06712372035595536</v>
+        <v>0.14946199681296191</v>
       </c>
       <c r="C37">
-        <v>0.1272070966638671</v>
+        <v>0.33662921590394418</v>
       </c>
       <c r="D37">
-        <v>0.2208118833581633</v>
+        <v>0.29183434634435901</v>
       </c>
       <c r="E37">
-        <v>0.2114662720038407</v>
+        <v>0.32082983152628147</v>
       </c>
       <c r="F37">
-        <v>0.1933223498168176</v>
+        <v>0.51964287399558406</v>
       </c>
       <c r="G37">
-        <v>0.2114115948780261</v>
+        <v>0.54707954475308473</v>
       </c>
       <c r="H37">
-        <v>0.3979938204352149</v>
+        <v>0.55715198824854428</v>
       </c>
       <c r="I37">
-        <v>0.3951815105900816</v>
+        <v>0.5559870997584947</v>
       </c>
       <c r="J37">
-        <v>0.38562907164682</v>
+        <v>0.59960778084734712</v>
       </c>
       <c r="K37">
-        <v>0.3548210150440567</v>
+        <v>0.65547059807049024</v>
       </c>
       <c r="L37">
-        <v>0.3541082907231</v>
+        <v>0.707829785725274</v>
       </c>
       <c r="M37">
-        <v>0.350011923660455</v>
+        <v>0.77809099688523264</v>
       </c>
       <c r="N37">
-        <v>0.3972751460511406</v>
+        <v>0.78046875177824038</v>
       </c>
       <c r="O37">
-        <v>0.441815262104426</v>
+        <v>0.79495019060900041</v>
       </c>
       <c r="P37">
-        <v>0.5000301383265465</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
-        </is>
+        <v>0.80253196754516765</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>52</v>
       </c>
       <c r="B38">
-        <v>0.07097459395452993</v>
+        <v>9.9967437938747516E-2</v>
       </c>
       <c r="C38">
-        <v>0.1341346374750731</v>
+        <v>0.2484942007802167</v>
       </c>
       <c r="D38">
-        <v>0.2276582597694146</v>
+        <v>0.25232743601790297</v>
       </c>
       <c r="E38">
-        <v>0.2080613621289629</v>
+        <v>0.29374815726366288</v>
       </c>
       <c r="F38">
-        <v>0.1940232340712603</v>
+        <v>0.47536304899512222</v>
       </c>
       <c r="G38">
-        <v>0.2046894891542714</v>
+        <v>0.36723805549985661</v>
       </c>
       <c r="H38">
-        <v>0.3786249718048764</v>
+        <v>0.27185677180853279</v>
       </c>
       <c r="I38">
-        <v>0.380882842692014</v>
+        <v>0.33173692902979829</v>
       </c>
       <c r="J38">
-        <v>0.3697840949454634</v>
+        <v>0.4056714459868237</v>
       </c>
       <c r="K38">
-        <v>0.3495308207269469</v>
+        <v>0.47809836823846508</v>
       </c>
       <c r="L38">
-        <v>0.3489075195046838</v>
+        <v>0.52325285876053373</v>
       </c>
       <c r="M38">
-        <v>0.3467535350346005</v>
+        <v>0.57142467459002455</v>
       </c>
       <c r="N38">
-        <v>0.3840979831199923</v>
+        <v>0.61444380368401885</v>
       </c>
       <c r="O38">
-        <v>0.4135188558521128</v>
+        <v>0.6364221033296299</v>
       </c>
       <c r="P38">
-        <v>0.469317506313921</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-        </is>
+        <v>0.64558818999748002</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>53</v>
       </c>
       <c r="B39">
-        <v>0.07312781216885915</v>
+        <v>9.5777054104029882E-2</v>
       </c>
       <c r="C39">
-        <v>0.1385980379417396</v>
+        <v>0.22252128298762169</v>
       </c>
       <c r="D39">
-        <v>0.2324817490564553</v>
+        <v>0.2193885566570225</v>
       </c>
       <c r="E39">
-        <v>0.219800650824664</v>
+        <v>0.2154762422409148</v>
       </c>
       <c r="F39">
-        <v>0.2005136844959313</v>
+        <v>0.33544217097186402</v>
       </c>
       <c r="G39">
-        <v>0.2159977120725463</v>
+        <v>0.27323018608714739</v>
       </c>
       <c r="H39">
-        <v>0.392024672819816</v>
+        <v>0.25962991359225479</v>
       </c>
       <c r="I39">
-        <v>0.3886624145198087</v>
+        <v>0.30752422669915391</v>
       </c>
       <c r="J39">
-        <v>0.3761863467946833</v>
+        <v>0.35341422243073328</v>
       </c>
       <c r="K39">
-        <v>0.3512552044744585</v>
+        <v>0.38806264757737718</v>
       </c>
       <c r="L39">
-        <v>0.3550666734474831</v>
+        <v>0.44208109468587198</v>
       </c>
       <c r="M39">
-        <v>0.3453046994587969</v>
+        <v>0.4510486974179197</v>
       </c>
       <c r="N39">
-        <v>0.3827495199269257</v>
+        <v>0.51073198384810259</v>
       </c>
       <c r="O39">
-        <v>0.4166101122363515</v>
+        <v>0.5564577433233393</v>
       </c>
       <c r="P39">
-        <v>0.4619329923383294</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-        </is>
+        <v>0.59112789448577308</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>54</v>
       </c>
       <c r="B40">
-        <v>0.07259329892980512</v>
+        <v>0.1429144158603998</v>
       </c>
       <c r="C40">
-        <v>0.1345921176015184</v>
+        <v>0.13457284710328929</v>
       </c>
       <c r="D40">
-        <v>0.2249689760872991</v>
+        <v>0.20601855466311339</v>
       </c>
       <c r="E40">
-        <v>0.210736283312182</v>
+        <v>0.27463672658901522</v>
       </c>
       <c r="F40">
-        <v>0.1988677515589792</v>
+        <v>0.37178756585934009</v>
       </c>
       <c r="G40">
-        <v>0.2101804318076824</v>
+        <v>0.37710369130849808</v>
       </c>
       <c r="H40">
-        <v>0.3568091301924503</v>
+        <v>0.44889819091072919</v>
       </c>
       <c r="I40">
-        <v>0.3678346252986001</v>
+        <v>0.54890570607273825</v>
       </c>
       <c r="J40">
-        <v>0.3650958239194347</v>
+        <v>0.61378312193818096</v>
       </c>
       <c r="K40">
-        <v>0.3101493435757403</v>
+        <v>0.62797781283787601</v>
       </c>
       <c r="L40">
-        <v>0.3245309266150815</v>
+        <v>0.65482470785099767</v>
       </c>
       <c r="M40">
-        <v>0.3207938442842878</v>
+        <v>0.65534098582094669</v>
       </c>
       <c r="N40">
-        <v>0.3450453601060306</v>
+        <v>0.69344180644365871</v>
       </c>
       <c r="O40">
-        <v>0.3775586785898598</v>
+        <v>0.74159895841984314</v>
       </c>
       <c r="P40">
-        <v>0.3885501509409019</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-        </is>
+        <v>0.82294851348201747</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>55</v>
       </c>
       <c r="B41">
-        <v>0.1490655056232214</v>
+        <v>0.1771686227038399</v>
       </c>
       <c r="C41">
-        <v>0.3365963060440381</v>
+        <v>0.50058384585817062</v>
       </c>
       <c r="D41">
-        <v>0.2970372341995525</v>
+        <v>0.49952058248617659</v>
       </c>
       <c r="E41">
-        <v>0.3247669300079282</v>
+        <v>0.58676013824674755</v>
       </c>
       <c r="F41">
-        <v>0.529167099466423</v>
+        <v>0.62212103675732466</v>
       </c>
       <c r="G41">
-        <v>0.5595924198457294</v>
+        <v>0.65150309886198177</v>
       </c>
       <c r="H41">
-        <v>0.5705356289432368</v>
+        <v>0.69282473757271179</v>
       </c>
       <c r="I41">
-        <v>0.5652848001488244</v>
+        <v>0.69316023661045978</v>
       </c>
       <c r="J41">
-        <v>0.6047920620891054</v>
+        <v>0.75619773748434715</v>
       </c>
       <c r="K41">
-        <v>0.6569646051951774</v>
+        <v>0.82453418725004601</v>
       </c>
       <c r="L41">
-        <v>0.7122697319011305</v>
+        <v>0.84871416536482081</v>
       </c>
       <c r="M41">
-        <v>0.7821650892338847</v>
+        <v>0.91196377866532363</v>
       </c>
       <c r="N41">
-        <v>0.7906385226784745</v>
+        <v>0.99710884997736793</v>
       </c>
       <c r="O41">
-        <v>0.8058037141067246</v>
+        <v>1.027946226212533</v>
       </c>
       <c r="P41">
-        <v>0.8168459668839667</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
-        </is>
+        <v>1.064364337808434</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>56</v>
       </c>
       <c r="B42">
-        <v>0.09514104987411134</v>
+        <v>6.130306461208046E-2</v>
       </c>
       <c r="C42">
-        <v>0.2447027264272519</v>
+        <v>0.61854879760624759</v>
       </c>
       <c r="D42">
-        <v>0.2467679860347173</v>
+        <v>0.54910856301852984</v>
       </c>
       <c r="E42">
-        <v>0.275373966014446</v>
+        <v>0.43017186652730199</v>
       </c>
       <c r="F42">
-        <v>0.458349144077238</v>
+        <v>0.41806648598825003</v>
       </c>
       <c r="G42">
-        <v>0.3594137291615068</v>
+        <v>0.45259408454769962</v>
       </c>
       <c r="H42">
-        <v>0.2799617608452066</v>
+        <v>0.42710028418750118</v>
       </c>
       <c r="I42">
-        <v>0.3318537540065947</v>
+        <v>0.45035823452942508</v>
       </c>
       <c r="J42">
-        <v>0.4038340993871228</v>
+        <v>0.50319324736793858</v>
       </c>
       <c r="K42">
-        <v>0.4780321290321683</v>
+        <v>0.51768070053990289</v>
       </c>
       <c r="L42">
-        <v>0.5281896288282524</v>
+        <v>0.54622328621411775</v>
       </c>
       <c r="M42">
-        <v>0.5710940168667763</v>
+        <v>0.61167091962006559</v>
       </c>
       <c r="N42">
-        <v>0.6073802445048522</v>
+        <v>0.64388741408078443</v>
       </c>
       <c r="O42">
-        <v>0.6281179758646911</v>
+        <v>0.65642310222002154</v>
       </c>
       <c r="P42">
-        <v>0.639330596537326</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-        </is>
+        <v>0.69377526467761508</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>57</v>
       </c>
       <c r="B43">
-        <v>0.09822444421045941</v>
+        <v>9.8092565479863933E-2</v>
       </c>
       <c r="C43">
-        <v>0.2271004104326129</v>
+        <v>0.23751057504353101</v>
       </c>
       <c r="D43">
-        <v>0.2171616570198887</v>
+        <v>0.38490958568749201</v>
       </c>
       <c r="E43">
-        <v>0.2235192977387298</v>
+        <v>0.45397972553260241</v>
       </c>
       <c r="F43">
-        <v>0.3460470624203867</v>
+        <v>0.36106889953267568</v>
       </c>
       <c r="G43">
-        <v>0.2839446117292472</v>
+        <v>0.36548058242166781</v>
       </c>
       <c r="H43">
-        <v>0.2584892996416457</v>
+        <v>0.40452797802305979</v>
       </c>
       <c r="I43">
-        <v>0.3064118626029328</v>
+        <v>0.45981669045018198</v>
       </c>
       <c r="J43">
-        <v>0.3584702385853312</v>
+        <v>0.56076189866103587</v>
       </c>
       <c r="K43">
-        <v>0.3875597346435118</v>
+        <v>0.55652535222060817</v>
       </c>
       <c r="L43">
-        <v>0.4343642889962925</v>
+        <v>0.57796767468150723</v>
       </c>
       <c r="M43">
-        <v>0.4449166534126942</v>
+        <v>0.59936167275839947</v>
       </c>
       <c r="N43">
-        <v>0.5026029824828034</v>
+        <v>0.64227493550983283</v>
       </c>
       <c r="O43">
-        <v>0.5549912584818245</v>
+        <v>0.67818689146705669</v>
       </c>
       <c r="P43">
-        <v>0.5851018650879896</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
-        </is>
-      </c>
-      <c r="B44">
-        <v>0.1429191901859555</v>
-      </c>
-      <c r="C44">
-        <v>0.1382917768582792</v>
-      </c>
-      <c r="D44">
-        <v>0.1978290497321425</v>
-      </c>
-      <c r="E44">
-        <v>0.2684406729439897</v>
-      </c>
-      <c r="F44">
-        <v>0.3693640016875882</v>
-      </c>
-      <c r="G44">
-        <v>0.3740444685379318</v>
-      </c>
-      <c r="H44">
-        <v>0.4506567953429677</v>
-      </c>
-      <c r="I44">
-        <v>0.5476639537084135</v>
-      </c>
-      <c r="J44">
-        <v>0.6118992102428737</v>
-      </c>
-      <c r="K44">
-        <v>0.6259271816037338</v>
-      </c>
-      <c r="L44">
-        <v>0.6581714211141718</v>
-      </c>
-      <c r="M44">
-        <v>0.66506838332847</v>
-      </c>
-      <c r="N44">
-        <v>0.7042118087948532</v>
-      </c>
-      <c r="O44">
-        <v>0.7502404264802121</v>
-      </c>
-      <c r="P44">
-        <v>0.8240497012345667</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>adj_snv_sder_c(1,3,5)_</t>
-        </is>
-      </c>
-      <c r="B45">
-        <v>0.1705025651057054</v>
-      </c>
-      <c r="C45">
-        <v>0.5079261556435934</v>
-      </c>
-      <c r="D45">
-        <v>0.497343947703733</v>
-      </c>
-      <c r="E45">
-        <v>0.5828731884114323</v>
-      </c>
-      <c r="F45">
-        <v>0.6204915893506291</v>
-      </c>
-      <c r="G45">
-        <v>0.6480264947355574</v>
-      </c>
-      <c r="H45">
-        <v>0.6930919175501906</v>
-      </c>
-      <c r="I45">
-        <v>0.696536154166538</v>
-      </c>
-      <c r="J45">
-        <v>0.7560593751624463</v>
-      </c>
-      <c r="K45">
-        <v>0.8206776079059649</v>
-      </c>
-      <c r="L45">
-        <v>0.851836769212291</v>
-      </c>
-      <c r="M45">
-        <v>0.9130858772949259</v>
-      </c>
-      <c r="N45">
-        <v>0.992293503755272</v>
-      </c>
-      <c r="O45">
-        <v>1.022746503372373</v>
-      </c>
-      <c r="P45">
-        <v>1.063017939789391</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>adj_snv_sder_c(2,3,15)_</t>
-        </is>
-      </c>
-      <c r="B46">
-        <v>0.05785073043397997</v>
-      </c>
-      <c r="C46">
-        <v>0.6065384398387017</v>
-      </c>
-      <c r="D46">
-        <v>0.5337321706532547</v>
-      </c>
-      <c r="E46">
-        <v>0.4140207501100426</v>
-      </c>
-      <c r="F46">
-        <v>0.4127102312907328</v>
-      </c>
-      <c r="G46">
-        <v>0.4422624187651038</v>
-      </c>
-      <c r="H46">
-        <v>0.4175135219742114</v>
-      </c>
-      <c r="I46">
-        <v>0.4461747467248345</v>
-      </c>
-      <c r="J46">
-        <v>0.492627000213079</v>
-      </c>
-      <c r="K46">
-        <v>0.5121428708115359</v>
-      </c>
-      <c r="L46">
-        <v>0.5452009976370192</v>
-      </c>
-      <c r="M46">
-        <v>0.6095662719269517</v>
-      </c>
-      <c r="N46">
-        <v>0.6370916423769</v>
-      </c>
-      <c r="O46">
-        <v>0.6503788765778507</v>
-      </c>
-      <c r="P46">
-        <v>0.691939455675543</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
-        </is>
-      </c>
-      <c r="B47">
-        <v>0.110541872057105</v>
-      </c>
-      <c r="C47">
-        <v>0.2505289486349514</v>
-      </c>
-      <c r="D47">
-        <v>0.3843532461328639</v>
-      </c>
-      <c r="E47">
-        <v>0.4660579052871431</v>
-      </c>
-      <c r="F47">
-        <v>0.3608401355829366</v>
-      </c>
-      <c r="G47">
-        <v>0.3679600456349216</v>
-      </c>
-      <c r="H47">
-        <v>0.3983615024108103</v>
-      </c>
-      <c r="I47">
-        <v>0.4492293443922828</v>
-      </c>
-      <c r="J47">
-        <v>0.5439030485689029</v>
-      </c>
-      <c r="K47">
-        <v>0.5503002294094868</v>
-      </c>
-      <c r="L47">
-        <v>0.5779980109062858</v>
-      </c>
-      <c r="M47">
-        <v>0.6056296989672674</v>
-      </c>
-      <c r="N47">
-        <v>0.6486172670868847</v>
-      </c>
-      <c r="O47">
-        <v>0.6798944894643668</v>
-      </c>
-      <c r="P47">
-        <v>0.7187812332221583</v>
+        <v>0.70857553279714702</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B2:P43">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
+      <formula>0.2</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
+      <formula>0.2</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>